--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="95">
   <si>
     <t>ID</t>
   </si>
@@ -158,27 +158,27 @@
     <t xml:space="preserve"> BODY SOLILING</t>
   </si>
   <si>
+    <t>SABITRA DEVI DAHAL</t>
+  </si>
+  <si>
+    <t>96 , BUDA VAYERA SUGAR VAYERA</t>
+  </si>
+  <si>
+    <t>GITBHADUR GURUNG</t>
+  </si>
+  <si>
+    <t>v4</t>
+  </si>
+  <si>
+    <t>SHRIMATI ROKAYA</t>
+  </si>
+  <si>
+    <t>v5</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>SABITRA DEVI DAHAL</t>
-  </si>
-  <si>
-    <t>96 , BUDA VAYERA SUGAR VAYERA</t>
-  </si>
-  <si>
-    <t>GITBHADUR GURUNG</t>
-  </si>
-  <si>
-    <t>v4</t>
-  </si>
-  <si>
-    <t>SHRIMATI ROKAYA</t>
-  </si>
-  <si>
-    <t>v5</t>
-  </si>
-  <si>
     <t>CHAN</t>
   </si>
   <si>
@@ -263,16 +263,43 @@
     <t>DHAL BDR THAMI</t>
   </si>
   <si>
+    <t>PASANG LAMA</t>
+  </si>
+  <si>
+    <t>BAM BAHADUR CHAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AGE VAYERA</t>
+  </si>
+  <si>
     <t>MOHAN CHAUDHARY</t>
   </si>
   <si>
     <t xml:space="preserve"> HEART ATTACK</t>
   </si>
   <si>
+    <t>RABITA PATEL</t>
+  </si>
+  <si>
+    <t>96 , RAMRO</t>
+  </si>
+  <si>
     <t>TAJNATH DHAKAL</t>
   </si>
   <si>
     <t xml:space="preserve"> OLD AGE</t>
+  </si>
+  <si>
+    <t>LATAKANCHA TAMANG</t>
+  </si>
+  <si>
+    <t>SAGAR MAHATO</t>
+  </si>
+  <si>
+    <t>KAMAN SINGH SARKI</t>
+  </si>
+  <si>
+    <t>CHANDRA BAHADUR NEPALI</t>
   </si>
 </sst>
 </file>
@@ -629,7 +656,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.855713" bestFit="true" customWidth="true" style="0"/>
@@ -650,12 +677,12 @@
     <col min="16" max="16" width="25.85083" bestFit="true" customWidth="true" style="0"/>
     <col min="17" max="17" width="56.557617" bestFit="true" customWidth="true" style="0"/>
     <col min="18" max="18" width="6.998291" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="8.140869" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="9.283447" bestFit="true" customWidth="true" style="0"/>
     <col min="20" max="20" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="21" max="21" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="22" max="22" width="6.998291" bestFit="true" customWidth="true" style="0"/>
     <col min="23" max="23" width="6.998291" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="6.998291" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="8.140869" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
@@ -1325,7 +1352,7 @@
         <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H11">
         <v>22</v>
@@ -1337,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11">
         <v>81</v>
@@ -1346,7 +1373,7 @@
         <v>32</v>
       </c>
       <c r="Q11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S11">
         <v>70000</v>
@@ -1387,7 +1414,7 @@
         <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H12">
         <v>42</v>
@@ -1402,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M12" t="s">
         <v>26</v>
@@ -1449,7 +1476,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -1467,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M13" t="s">
         <v>32</v>
@@ -1517,10 +1544,10 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
         <v>53</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
       </c>
       <c r="H14">
         <v>53</v>
@@ -1561,10 +1588,10 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H15">
         <v>54</v>
@@ -1629,10 +1656,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" t="s">
         <v>53</v>
-      </c>
-      <c r="G16" t="s">
-        <v>47</v>
       </c>
       <c r="H16">
         <v>22</v>
@@ -1697,10 +1724,10 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
         <v>53</v>
-      </c>
-      <c r="G17" t="s">
-        <v>47</v>
       </c>
       <c r="H17">
         <v>24</v>
@@ -1765,10 +1792,10 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" t="s">
         <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
       </c>
       <c r="H18">
         <v>27</v>
@@ -1836,10 +1863,10 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" t="s">
         <v>53</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
       </c>
       <c r="H19">
         <v>72</v>
@@ -1904,10 +1931,10 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" t="s">
         <v>53</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
       <c r="H20">
         <v>26</v>
@@ -1960,10 +1987,10 @@
         <v>5</v>
       </c>
       <c r="F21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" t="s">
         <v>53</v>
-      </c>
-      <c r="G21" t="s">
-        <v>47</v>
       </c>
       <c r="H21">
         <v>28</v>
@@ -2025,10 +2052,10 @@
         <v>3</v>
       </c>
       <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" t="s">
         <v>53</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
       </c>
       <c r="H22">
         <v>22</v>
@@ -2090,10 +2117,10 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" t="s">
         <v>53</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
       </c>
       <c r="H23">
         <v>51</v>
@@ -2155,10 +2182,10 @@
         <v>6</v>
       </c>
       <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" t="s">
         <v>53</v>
-      </c>
-      <c r="G24" t="s">
-        <v>47</v>
       </c>
       <c r="H24">
         <v>53</v>
@@ -2220,10 +2247,10 @@
         <v>13</v>
       </c>
       <c r="F25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" t="s">
         <v>53</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
       </c>
       <c r="H25">
         <v>94</v>
@@ -2285,10 +2312,10 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" t="s">
         <v>53</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
       </c>
       <c r="H26">
         <v>64</v>
@@ -2350,10 +2377,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" t="s">
         <v>53</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
       </c>
       <c r="H27">
         <v>64</v>
@@ -2418,10 +2445,10 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" t="s">
         <v>53</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
       </c>
       <c r="H28">
         <v>51</v>
@@ -2483,10 +2510,10 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" t="s">
         <v>53</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
       </c>
       <c r="H29">
         <v>51</v>
@@ -2533,28 +2560,28 @@
     </row>
     <row r="30" spans="1:24">
       <c r="A30">
-        <v>5266</v>
+        <v>5146</v>
       </c>
       <c r="B30">
-        <v>7108</v>
+        <v>4201</v>
       </c>
       <c r="C30">
-        <v>70901</v>
+        <v>40204</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" t="s">
         <v>53</v>
       </c>
-      <c r="G30" t="s">
-        <v>47</v>
-      </c>
       <c r="H30">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
@@ -2572,57 +2599,48 @@
         <v>26</v>
       </c>
       <c r="N30">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="O30" t="s">
-        <v>28</v>
-      </c>
-      <c r="P30" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="31" spans="1:24">
       <c r="A31">
-        <v>5517</v>
+        <v>5150</v>
       </c>
       <c r="B31">
-        <v>3387</v>
+        <v>6204</v>
       </c>
       <c r="C31">
-        <v>30608</v>
+        <v>60608</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" t="s">
         <v>53</v>
       </c>
-      <c r="G31" t="s">
-        <v>47</v>
-      </c>
       <c r="H31">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
@@ -2634,37 +2652,486 @@
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M31" t="s">
         <v>26</v>
       </c>
       <c r="N31">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O31" t="s">
         <v>28</v>
       </c>
       <c r="P31" t="s">
+        <v>84</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24">
+      <c r="A32">
+        <v>5266</v>
+      </c>
+      <c r="B32">
+        <v>7108</v>
+      </c>
+      <c r="C32">
+        <v>70901</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
         <v>85</v>
       </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32">
+        <v>65</v>
+      </c>
+      <c r="O32" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" t="s">
+        <v>86</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24">
+      <c r="A33">
+        <v>5386</v>
+      </c>
+      <c r="B33">
+        <v>2208</v>
+      </c>
+      <c r="C33">
+        <v>20614</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33">
+        <v>28</v>
+      </c>
+      <c r="I33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
+        <v>87</v>
+      </c>
+      <c r="M33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33">
+        <v>24</v>
+      </c>
+      <c r="O33" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>88</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24">
+      <c r="A34">
+        <v>5517</v>
+      </c>
+      <c r="B34">
+        <v>3387</v>
+      </c>
+      <c r="C34">
+        <v>30608</v>
+      </c>
+      <c r="D34">
+        <v>30</v>
+      </c>
+      <c r="E34">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34">
+        <v>94</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
+        <v>89</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34">
+        <v>72</v>
+      </c>
+      <c r="O34" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" t="s">
+        <v>90</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24">
+      <c r="A35">
+        <v>5524</v>
+      </c>
+      <c r="B35">
+        <v>3209</v>
+      </c>
+      <c r="C35">
+        <v>70803</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35">
+        <v>57</v>
+      </c>
+      <c r="I35" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>2082</v>
+      </c>
+      <c r="L35" t="s">
+        <v>91</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35">
+        <v>84</v>
+      </c>
+      <c r="O35" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" t="s">
+        <v>90</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24">
+      <c r="A36">
+        <v>5892</v>
+      </c>
+      <c r="B36">
+        <v>2209</v>
+      </c>
+      <c r="C36">
+        <v>20703</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36">
+        <v>22</v>
+      </c>
+      <c r="F36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36">
+        <v>26</v>
+      </c>
+      <c r="I36" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>92</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36">
+        <v>14</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="S36">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24">
+      <c r="A37">
+        <v>5998</v>
+      </c>
+      <c r="B37">
+        <v>6204</v>
+      </c>
+      <c r="C37">
+        <v>60608</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37">
+        <v>63</v>
+      </c>
+      <c r="I37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>93</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37">
+        <v>68</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24">
+      <c r="A38">
+        <v>6013</v>
+      </c>
+      <c r="B38">
+        <v>6204</v>
+      </c>
+      <c r="C38">
+        <v>60608</v>
+      </c>
+      <c r="D38">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H38">
+        <v>61</v>
+      </c>
+      <c r="I38" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>94</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38">
+        <v>70</v>
+      </c>
+      <c r="O38" t="s">
+        <v>32</v>
+      </c>
+      <c r="S38">
+        <v>20000</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>96000</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
   <si>
     <t>ID</t>
   </si>
@@ -176,66 +176,66 @@
     <t>v5</t>
   </si>
   <si>
+    <t>CHAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> , 96 , BUDI AAMA</t>
+  </si>
+  <si>
+    <t>POTA KUMARI KC</t>
+  </si>
+  <si>
+    <t>96 , UMER PUGERA MRITYU VAYEKO</t>
+  </si>
+  <si>
+    <t>BHAGAWATI NEUPANE</t>
+  </si>
+  <si>
+    <t>DILIP DAHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MIRGAULA KO KARNA</t>
+  </si>
+  <si>
+    <t>LAXMI GUPTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HIP MA GHAU</t>
+  </si>
+  <si>
+    <t>HIP MA GHAU VAYERA ACHANAK 1 WEEK MA MRITUBVAYO</t>
+  </si>
+  <si>
+    <t>YAGYA RAJ JOSHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4 </t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>CHAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> , 96 , BUDI AAMA</t>
-  </si>
-  <si>
-    <t>POTA KUMARI KC</t>
-  </si>
-  <si>
-    <t>96 , UMER PUGERA MRITYU VAYEKO</t>
-  </si>
-  <si>
-    <t>BHAGAWATI NEUPANE</t>
+    <t>JALIL ANSARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DIMAG KO NASA FATERA</t>
+  </si>
+  <si>
+    <t>JITAN PANDIT</t>
+  </si>
+  <si>
+    <t>JIBAT LAL SHAH</t>
+  </si>
+  <si>
+    <t>SUJAN UDASH</t>
   </si>
   <si>
     <t xml:space="preserve">3 </t>
   </si>
   <si>
-    <t>DILIP DAHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MIRGAULA KO KARNA</t>
-  </si>
-  <si>
-    <t>LAXMI GUPTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HIP MA GHAU</t>
-  </si>
-  <si>
-    <t>HIP MA GHAU VAYERA ACHANAK 1 WEEK MA MRITUBVAYO</t>
-  </si>
-  <si>
-    <t>YAGYA RAJ JOSHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4 </t>
-  </si>
-  <si>
-    <t>JALIL ANSARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIMAG KO NASA FATERA</t>
-  </si>
-  <si>
-    <t>JITAN PANDIT</t>
-  </si>
-  <si>
-    <t>JIBAT LAL SHAH</t>
-  </si>
-  <si>
-    <t>SUJAN UDASH</t>
-  </si>
-  <si>
     <t>SURYA BAHADUR TAMANG</t>
   </si>
   <si>
@@ -300,6 +300,57 @@
   </si>
   <si>
     <t>CHANDRA BAHADUR NEPALI</t>
+  </si>
+  <si>
+    <t>JHALAK BAHADUR THAPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BRIDHABASTHA</t>
+  </si>
+  <si>
+    <t>AMBIKA SHARMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OLD AGE MULTI ORGAN FAIL</t>
+  </si>
+  <si>
+    <t>96 , BUDO</t>
+  </si>
+  <si>
+    <t>DEV BADHUR CHETTRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KIDDNI FAIL</t>
+  </si>
+  <si>
+    <t>RATAN DEVI SHAH</t>
+  </si>
+  <si>
+    <t>HUMKALA RAYMAJHI</t>
+  </si>
+  <si>
+    <t>SHOVAKHAR PANDEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INFECTION ON HAND</t>
+  </si>
+  <si>
+    <t>PARBATI DEVI JAISI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LADAKO</t>
+  </si>
+  <si>
+    <t>SURYAMAN BALAMI</t>
+  </si>
+  <si>
+    <t>0, 8</t>
+  </si>
+  <si>
+    <t>TULSI DEVI KHADKA</t>
+  </si>
+  <si>
+    <t>96 , UMER LAGERA DEATH VAYEKO, UMER LAGERA MIRTYU BHAKO</t>
   </si>
 </sst>
 </file>
@@ -656,7 +707,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.855713" bestFit="true" customWidth="true" style="0"/>
@@ -674,8 +725,8 @@
     <col min="13" max="13" width="5.855713" bestFit="true" customWidth="true" style="0"/>
     <col min="14" max="14" width="5.855713" bestFit="true" customWidth="true" style="0"/>
     <col min="15" max="15" width="5.855713" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="25.85083" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="56.557617" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="30.563965" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="65.983887" bestFit="true" customWidth="true" style="0"/>
     <col min="18" max="18" width="6.998291" bestFit="true" customWidth="true" style="0"/>
     <col min="19" max="19" width="9.283447" bestFit="true" customWidth="true" style="0"/>
     <col min="20" max="20" width="8.140869" bestFit="true" customWidth="true" style="0"/>
@@ -1145,7 +1196,7 @@
         <v>2782</v>
       </c>
       <c r="B8">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="C8">
         <v>30608</v>
@@ -1402,7 +1453,7 @@
         <v>4103</v>
       </c>
       <c r="C12">
-        <v>40903</v>
+        <v>40602</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1547,7 +1598,7 @@
         <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H14">
         <v>53</v>
@@ -1562,13 +1613,13 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M14" t="s">
         <v>32</v>
       </c>
       <c r="Q14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1606,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M15" t="s">
         <v>32</v>
@@ -1618,7 +1669,7 @@
         <v>28</v>
       </c>
       <c r="Q15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S15">
         <v>150000</v>
@@ -1659,7 +1710,7 @@
         <v>52</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H16">
         <v>22</v>
@@ -1674,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16" t="s">
         <v>32</v>
@@ -1684,9 +1735,6 @@
       </c>
       <c r="O16" t="s">
         <v>32</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>59</v>
       </c>
       <c r="S16">
         <v>800000</v>
@@ -1727,7 +1775,7 @@
         <v>52</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H17">
         <v>24</v>
@@ -1742,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -1754,7 +1802,7 @@
         <v>32</v>
       </c>
       <c r="P17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="S17">
         <v>60000</v>
@@ -1795,7 +1843,7 @@
         <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H18">
         <v>27</v>
@@ -1810,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M18" t="s">
         <v>32</v>
@@ -1822,10 +1870,10 @@
         <v>28</v>
       </c>
       <c r="P18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S18">
         <v>300000</v>
@@ -1866,7 +1914,7 @@
         <v>52</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H19">
         <v>72</v>
@@ -1881,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M19" t="s">
         <v>26</v>
@@ -1890,10 +1938,10 @@
         <v>95</v>
       </c>
       <c r="O19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S19">
         <v>30000</v>
@@ -1934,7 +1982,7 @@
         <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H20">
         <v>26</v>
@@ -1949,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M20" t="s">
         <v>26</v>
@@ -1961,7 +2009,7 @@
         <v>28</v>
       </c>
       <c r="P20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S20">
         <v>40000</v>
@@ -1990,7 +2038,7 @@
         <v>52</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H21">
         <v>28</v>
@@ -2005,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M21" t="s">
         <v>26</v>
@@ -2055,7 +2103,7 @@
         <v>52</v>
       </c>
       <c r="G22" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H22">
         <v>22</v>
@@ -2070,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M22" t="s">
         <v>26</v>
@@ -2120,7 +2168,7 @@
         <v>52</v>
       </c>
       <c r="G23" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H23">
         <v>51</v>
@@ -2135,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M23" t="s">
         <v>26</v>
@@ -2144,7 +2192,7 @@
         <v>20</v>
       </c>
       <c r="O23" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="S23">
         <v>55000</v>
@@ -2185,7 +2233,7 @@
         <v>52</v>
       </c>
       <c r="G24" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H24">
         <v>53</v>
@@ -2250,7 +2298,7 @@
         <v>52</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H25">
         <v>94</v>
@@ -2315,7 +2363,7 @@
         <v>52</v>
       </c>
       <c r="G26" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H26">
         <v>64</v>
@@ -2380,7 +2428,7 @@
         <v>52</v>
       </c>
       <c r="G27" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H27">
         <v>64</v>
@@ -2448,7 +2496,7 @@
         <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H28">
         <v>51</v>
@@ -2513,7 +2561,7 @@
         <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H29">
         <v>51</v>
@@ -2578,7 +2626,7 @@
         <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H30">
         <v>43</v>
@@ -2637,7 +2685,7 @@
         <v>52</v>
       </c>
       <c r="G31" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H31">
         <v>64</v>
@@ -2705,7 +2753,7 @@
         <v>52</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H32">
         <v>74</v>
@@ -2773,7 +2821,7 @@
         <v>52</v>
       </c>
       <c r="G33" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H33">
         <v>28</v>
@@ -2841,7 +2889,7 @@
         <v>52</v>
       </c>
       <c r="G34" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H34">
         <v>94</v>
@@ -2897,7 +2945,7 @@
         <v>3209</v>
       </c>
       <c r="C35">
-        <v>70803</v>
+        <v>30803</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -2909,7 +2957,7 @@
         <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H35">
         <v>57</v>
@@ -2977,7 +3025,7 @@
         <v>52</v>
       </c>
       <c r="G36" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H36">
         <v>26</v>
@@ -3027,7 +3075,7 @@
         <v>52</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H37">
         <v>63</v>
@@ -3089,7 +3137,7 @@
         <v>52</v>
       </c>
       <c r="G38" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H38">
         <v>61</v>
@@ -3132,6 +3180,600 @@
       </c>
       <c r="X38">
         <v>96000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24">
+      <c r="A39">
+        <v>6450</v>
+      </c>
+      <c r="B39">
+        <v>1101</v>
+      </c>
+      <c r="C39">
+        <v>10207</v>
+      </c>
+      <c r="D39">
+        <v>7</v>
+      </c>
+      <c r="E39">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39">
+        <v>11</v>
+      </c>
+      <c r="I39" t="s">
+        <v>26</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>95</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39">
+        <v>73</v>
+      </c>
+      <c r="O39" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" t="s">
+        <v>96</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24">
+      <c r="A40">
+        <v>6671</v>
+      </c>
+      <c r="B40">
+        <v>4108</v>
+      </c>
+      <c r="C40">
+        <v>41003</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H40">
+        <v>42</v>
+      </c>
+      <c r="I40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>97</v>
+      </c>
+      <c r="M40" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40">
+        <v>98</v>
+      </c>
+      <c r="O40" t="s">
+        <v>28</v>
+      </c>
+      <c r="P40" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>99</v>
+      </c>
+      <c r="S40">
+        <v>18000</v>
+      </c>
+      <c r="T40">
+        <v>8000</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24">
+      <c r="A41">
+        <v>7110</v>
+      </c>
+      <c r="B41">
+        <v>7109</v>
+      </c>
+      <c r="C41">
+        <v>70909</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>30</v>
+      </c>
+      <c r="F41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
+        <v>100</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41">
+        <v>46</v>
+      </c>
+      <c r="O41" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" t="s">
+        <v>101</v>
+      </c>
+      <c r="S41">
+        <v>200000</v>
+      </c>
+      <c r="T41">
+        <v>20000</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>15000</v>
+      </c>
+      <c r="W41">
+        <v>12000</v>
+      </c>
+      <c r="X41">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24">
+      <c r="A42">
+        <v>7225</v>
+      </c>
+      <c r="B42">
+        <v>2101</v>
+      </c>
+      <c r="C42">
+        <v>20110</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>36</v>
+      </c>
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42">
+        <v>22</v>
+      </c>
+      <c r="I42" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>102</v>
+      </c>
+      <c r="M42" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42">
+        <v>53</v>
+      </c>
+      <c r="O42" t="s">
+        <v>32</v>
+      </c>
+      <c r="S42">
+        <v>1400000</v>
+      </c>
+      <c r="T42" t="s">
+        <v>79</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24">
+      <c r="A43">
+        <v>7464</v>
+      </c>
+      <c r="B43">
+        <v>5105</v>
+      </c>
+      <c r="C43">
+        <v>50901</v>
+      </c>
+      <c r="D43">
+        <v>9</v>
+      </c>
+      <c r="E43">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43">
+        <v>54</v>
+      </c>
+      <c r="I43" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>103</v>
+      </c>
+      <c r="M43" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43">
+        <v>71</v>
+      </c>
+      <c r="O43" t="s">
+        <v>32</v>
+      </c>
+      <c r="S43">
+        <v>100000</v>
+      </c>
+      <c r="T43">
+        <v>25000</v>
+      </c>
+      <c r="U43">
+        <v>16000</v>
+      </c>
+      <c r="V43">
+        <v>6000</v>
+      </c>
+      <c r="W43">
+        <v>7000</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24">
+      <c r="A44">
+        <v>7585</v>
+      </c>
+      <c r="B44">
+        <v>5205</v>
+      </c>
+      <c r="C44">
+        <v>50901</v>
+      </c>
+      <c r="D44">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>28</v>
+      </c>
+      <c r="F44" t="s">
+        <v>52</v>
+      </c>
+      <c r="G44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44">
+        <v>51</v>
+      </c>
+      <c r="I44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44">
+        <v>92</v>
+      </c>
+      <c r="O44" t="s">
+        <v>28</v>
+      </c>
+      <c r="P44" t="s">
+        <v>105</v>
+      </c>
+      <c r="S44">
+        <v>150000</v>
+      </c>
+      <c r="T44" t="s">
+        <v>79</v>
+      </c>
+      <c r="U44" t="s">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24">
+      <c r="A45">
+        <v>7595</v>
+      </c>
+      <c r="B45">
+        <v>5205</v>
+      </c>
+      <c r="C45">
+        <v>50901</v>
+      </c>
+      <c r="D45">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>31</v>
+      </c>
+      <c r="F45" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45">
+        <v>51</v>
+      </c>
+      <c r="I45" t="s">
+        <v>26</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>106</v>
+      </c>
+      <c r="M45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45">
+        <v>95</v>
+      </c>
+      <c r="O45" t="s">
+        <v>28</v>
+      </c>
+      <c r="P45" t="s">
+        <v>107</v>
+      </c>
+      <c r="S45">
+        <v>55000</v>
+      </c>
+      <c r="T45">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24">
+      <c r="A46">
+        <v>8047</v>
+      </c>
+      <c r="B46">
+        <v>3104</v>
+      </c>
+      <c r="C46">
+        <v>30512</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>37</v>
+      </c>
+      <c r="F46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46">
+        <v>57</v>
+      </c>
+      <c r="I46" t="s">
+        <v>26</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>2081</v>
+      </c>
+      <c r="L46" t="s">
+        <v>108</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46">
+        <v>75</v>
+      </c>
+      <c r="O46" t="s">
+        <v>26</v>
+      </c>
+      <c r="S46">
+        <v>50000</v>
+      </c>
+      <c r="T46">
+        <v>20000</v>
+      </c>
+      <c r="U46">
+        <v>80000</v>
+      </c>
+      <c r="V46">
+        <v>2000</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24">
+      <c r="A47">
+        <v>8293</v>
+      </c>
+      <c r="B47">
+        <v>7105</v>
+      </c>
+      <c r="C47">
+        <v>70601</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>33</v>
+      </c>
+      <c r="F47" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47">
+        <v>72</v>
+      </c>
+      <c r="I47" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>109</v>
+      </c>
+      <c r="L47" t="s">
+        <v>110</v>
+      </c>
+      <c r="M47" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47">
+        <v>72</v>
+      </c>
+      <c r="O47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>111</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -215,18 +215,18 @@
     <t xml:space="preserve"> 4 </t>
   </si>
   <si>
+    <t>JALIL ANSARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DIMAG KO NASA FATERA</t>
+  </si>
+  <si>
+    <t>JITAN PANDIT</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>JALIL ANSARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DIMAG KO NASA FATERA</t>
-  </si>
-  <si>
-    <t>JITAN PANDIT</t>
-  </si>
-  <si>
     <t>JIBAT LAL SHAH</t>
   </si>
   <si>
@@ -302,55 +302,58 @@
     <t>CHANDRA BAHADUR NEPALI</t>
   </si>
   <si>
+    <t>AMBIKA SHARMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OLD AGE MULTI ORGAN FAIL</t>
+  </si>
+  <si>
+    <t>96 , BUDO</t>
+  </si>
+  <si>
+    <t>DHOLE RANA</t>
+  </si>
+  <si>
+    <t>DEV BADHUR CHETTRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KIDDNI FAIL</t>
+  </si>
+  <si>
+    <t>RATAN DEVI SHAH</t>
+  </si>
+  <si>
+    <t>HUMKALA RAYMAJHI</t>
+  </si>
+  <si>
+    <t>SHOVAKHAR PANDEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INFECTION ON HAND</t>
+  </si>
+  <si>
+    <t>PARBATI DEVI JAISI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LADAKO</t>
+  </si>
+  <si>
+    <t>SURYAMAN BALAMI</t>
+  </si>
+  <si>
+    <t>0, 8</t>
+  </si>
+  <si>
+    <t>TULSI DEVI KHADKA</t>
+  </si>
+  <si>
+    <t>96 , UMER LAGERA DEATH VAYEKO, UMER LAGERA MIRTYU BHAKO</t>
+  </si>
+  <si>
     <t>JHALAK BAHADUR THAPA</t>
   </si>
   <si>
     <t xml:space="preserve"> BRIDHABASTHA</t>
-  </si>
-  <si>
-    <t>AMBIKA SHARMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OLD AGE MULTI ORGAN FAIL</t>
-  </si>
-  <si>
-    <t>96 , BUDO</t>
-  </si>
-  <si>
-    <t>DEV BADHUR CHETTRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KIDDNI FAIL</t>
-  </si>
-  <si>
-    <t>RATAN DEVI SHAH</t>
-  </si>
-  <si>
-    <t>HUMKALA RAYMAJHI</t>
-  </si>
-  <si>
-    <t>SHOVAKHAR PANDEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INFECTION ON HAND</t>
-  </si>
-  <si>
-    <t>PARBATI DEVI JAISI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LADAKO</t>
-  </si>
-  <si>
-    <t>SURYAMAN BALAMI</t>
-  </si>
-  <si>
-    <t>0, 8</t>
-  </si>
-  <si>
-    <t>TULSI DEVI KHADKA</t>
-  </si>
-  <si>
-    <t>96 , UMER LAGERA DEATH VAYEKO, UMER LAGERA MIRTYU BHAKO</t>
   </si>
 </sst>
 </file>
@@ -707,7 +710,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:X48"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.855713" bestFit="true" customWidth="true" style="0"/>
@@ -1982,22 +1985,22 @@
         <v>52</v>
       </c>
       <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
         <v>66</v>
-      </c>
-      <c r="H20">
-        <v>26</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>67</v>
       </c>
       <c r="M20" t="s">
         <v>26</v>
@@ -2009,7 +2012,7 @@
         <v>28</v>
       </c>
       <c r="P20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="S20">
         <v>40000</v>
@@ -2038,7 +2041,7 @@
         <v>52</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="H21">
         <v>28</v>
@@ -2053,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M21" t="s">
         <v>26</v>
@@ -2103,7 +2106,7 @@
         <v>52</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H22">
         <v>22</v>
@@ -2168,7 +2171,7 @@
         <v>52</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H23">
         <v>51</v>
@@ -2233,7 +2236,7 @@
         <v>52</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H24">
         <v>53</v>
@@ -2298,7 +2301,7 @@
         <v>52</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H25">
         <v>94</v>
@@ -2363,7 +2366,7 @@
         <v>52</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H26">
         <v>64</v>
@@ -2428,7 +2431,7 @@
         <v>52</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H27">
         <v>64</v>
@@ -2496,7 +2499,7 @@
         <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H28">
         <v>51</v>
@@ -2561,7 +2564,7 @@
         <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H29">
         <v>51</v>
@@ -2626,7 +2629,7 @@
         <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H30">
         <v>43</v>
@@ -2685,7 +2688,7 @@
         <v>52</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H31">
         <v>64</v>
@@ -2753,7 +2756,7 @@
         <v>52</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H32">
         <v>74</v>
@@ -2821,7 +2824,7 @@
         <v>52</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H33">
         <v>28</v>
@@ -2889,7 +2892,7 @@
         <v>52</v>
       </c>
       <c r="G34" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H34">
         <v>94</v>
@@ -2957,7 +2960,7 @@
         <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H35">
         <v>57</v>
@@ -3025,7 +3028,7 @@
         <v>52</v>
       </c>
       <c r="G36" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H36">
         <v>26</v>
@@ -3075,7 +3078,7 @@
         <v>52</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H37">
         <v>63</v>
@@ -3184,28 +3187,28 @@
     </row>
     <row r="39" spans="1:24">
       <c r="A39">
-        <v>6450</v>
+        <v>6671</v>
       </c>
       <c r="B39">
-        <v>1101</v>
+        <v>4108</v>
       </c>
       <c r="C39">
-        <v>10207</v>
+        <v>41003</v>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F39" t="s">
         <v>52</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H39">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
@@ -3220,10 +3223,10 @@
         <v>95</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N39">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="O39" t="s">
         <v>28</v>
@@ -3231,11 +3234,14 @@
       <c r="P39" t="s">
         <v>96</v>
       </c>
+      <c r="Q39" t="s">
+        <v>97</v>
+      </c>
       <c r="S39">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -3247,33 +3253,33 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="40" spans="1:24">
       <c r="A40">
-        <v>6671</v>
+        <v>6967</v>
       </c>
       <c r="B40">
-        <v>4108</v>
+        <v>6106</v>
       </c>
       <c r="C40">
-        <v>41003</v>
+        <v>60806</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F40" t="s">
         <v>52</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H40">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3285,28 +3291,25 @@
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M40" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N40">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="O40" t="s">
         <v>28</v>
       </c>
       <c r="P40" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="S40">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -3318,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -3356,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M41" t="s">
         <v>26</v>
@@ -3368,7 +3371,7 @@
         <v>28</v>
       </c>
       <c r="P41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S41">
         <v>200000</v>
@@ -3409,7 +3412,7 @@
         <v>52</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H42">
         <v>22</v>
@@ -3424,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M42" t="s">
         <v>32</v>
@@ -3474,7 +3477,7 @@
         <v>52</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H43">
         <v>54</v>
@@ -3489,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M43" t="s">
         <v>32</v>
@@ -3539,7 +3542,7 @@
         <v>52</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H44">
         <v>51</v>
@@ -3554,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M44" t="s">
         <v>26</v>
@@ -3566,7 +3569,7 @@
         <v>28</v>
       </c>
       <c r="P44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S44">
         <v>150000</v>
@@ -3607,7 +3610,7 @@
         <v>52</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H45">
         <v>51</v>
@@ -3622,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M45" t="s">
         <v>32</v>
@@ -3634,7 +3637,7 @@
         <v>28</v>
       </c>
       <c r="P45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S45">
         <v>55000</v>
@@ -3663,7 +3666,7 @@
         <v>52</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H46">
         <v>57</v>
@@ -3678,7 +3681,7 @@
         <v>2081</v>
       </c>
       <c r="L46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M46" t="s">
         <v>26</v>
@@ -3728,7 +3731,7 @@
         <v>52</v>
       </c>
       <c r="G47" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H47">
         <v>72</v>
@@ -3740,10 +3743,10 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
+        <v>108</v>
+      </c>
+      <c r="L47" t="s">
         <v>109</v>
-      </c>
-      <c r="L47" t="s">
-        <v>110</v>
       </c>
       <c r="M47" t="s">
         <v>32</v>
@@ -3755,24 +3758,92 @@
         <v>44</v>
       </c>
       <c r="Q47" t="s">
+        <v>110</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24">
+      <c r="A48">
+        <v>8786</v>
+      </c>
+      <c r="B48">
+        <v>1101</v>
+      </c>
+      <c r="C48">
+        <v>10207</v>
+      </c>
+      <c r="D48">
+        <v>7</v>
+      </c>
+      <c r="E48">
+        <v>18</v>
+      </c>
+      <c r="F48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" t="s">
+        <v>69</v>
+      </c>
+      <c r="H48">
+        <v>11</v>
+      </c>
+      <c r="I48" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48" t="s">
         <v>111</v>
       </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48">
+        <v>73</v>
+      </c>
+      <c r="O48" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" t="s">
+        <v>112</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
         <v>0</v>
       </c>
     </row>

--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-10-29\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E35B868-8B36-43E5-B2A7-BDC9E2923CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6217A9B0-6ED1-454D-9148-8B78B7487611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="185">
   <si>
     <t>ID</t>
   </si>
@@ -397,6 +397,12 @@
   </si>
   <si>
     <t>CHANDRA BAHADUR NEPALI</t>
+  </si>
+  <si>
+    <t>a4d2f9c1-dadc-4994-a90c-224920228ed1</t>
+  </si>
+  <si>
+    <t>SHANTA MAYA BASNET</t>
   </si>
   <si>
     <t>8345e2f4-0393-4982-a302-038fc40704be</t>
@@ -932,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1034,31 +1040,31 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>770</v>
+        <v>6671</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="C2">
-        <v>5104</v>
+        <v>4108</v>
       </c>
       <c r="D2">
-        <v>50703</v>
+        <v>41003</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1070,25 +1076,28 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="P2">
         <v>96</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>126</v>
+      </c>
+      <c r="R2" t="s">
+        <v>127</v>
       </c>
       <c r="T2">
-        <v>300000</v>
+        <v>18000</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -1100,36 +1109,36 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>992</v>
+        <v>5150</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="C3">
-        <v>3201</v>
+        <v>6204</v>
       </c>
       <c r="D3">
-        <v>30102</v>
+        <v>60608</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1141,16 +1150,19 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
       <c r="O3">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>4</v>
+        <v>96</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>106</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -1158,8 +1170,8 @@
       <c r="U3">
         <v>0</v>
       </c>
-      <c r="V3" t="s">
-        <v>34</v>
+      <c r="V3">
+        <v>0</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -1173,31 +1185,31 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1302</v>
+        <v>3683</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>3111</v>
+        <v>1415</v>
       </c>
       <c r="D4">
-        <v>31101</v>
+        <v>11213</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="H4" t="s">
         <v>26</v>
       </c>
       <c r="I4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1209,25 +1221,22 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="N4">
         <v>2</v>
       </c>
       <c r="O4">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>96</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="U4">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -1244,31 +1253,31 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2341</v>
+        <v>10769</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>175</v>
       </c>
       <c r="C5">
-        <v>1317</v>
+        <v>2103</v>
       </c>
       <c r="D5">
-        <v>11307</v>
+        <v>20206</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>117</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1276,20 +1285,26 @@
       <c r="K5">
         <v>1</v>
       </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>176</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="R5" t="s">
+        <v>177</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -1301,36 +1316,39 @@
         <v>0</v>
       </c>
       <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2442</v>
+        <v>4581</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="C6">
-        <v>2310</v>
+        <v>6202</v>
       </c>
       <c r="D6">
-        <v>20612</v>
+        <v>60404</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1339,25 +1357,28 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
       <c r="O6">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="P6">
-        <v>96</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="T6">
-        <v>15000</v>
+        <v>20000</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1366,36 +1387,36 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2585</v>
+        <v>3356</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>7206</v>
+        <v>5102</v>
       </c>
       <c r="D7">
-        <v>70811</v>
+        <v>50601</v>
       </c>
       <c r="E7">
         <v>7</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
         <v>26</v>
       </c>
       <c r="I7">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1407,63 +1428,42 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>80</v>
-      </c>
-      <c r="P7">
-        <v>7</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="R7" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2591</v>
+        <v>6013</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C8">
-        <v>7106</v>
+        <v>6204</v>
       </c>
       <c r="D8">
-        <v>70811</v>
+        <v>60608</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="H8" t="s">
         <v>26</v>
       </c>
       <c r="I8">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1475,63 +1475,63 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
       <c r="O8">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8">
         <v>20000</v>
       </c>
       <c r="U8">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2634</v>
+        <v>2782</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9">
-        <v>1109</v>
+        <v>3206</v>
       </c>
       <c r="D9">
-        <v>11214</v>
+        <v>30604</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
         <v>26</v>
       </c>
       <c r="I9">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1543,51 +1543,63 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
       <c r="O9">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="P9">
-        <v>96</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="T9">
-        <v>15000</v>
+        <v>285000</v>
+      </c>
+      <c r="U9">
+        <v>115000</v>
+      </c>
+      <c r="V9">
+        <v>75000</v>
+      </c>
+      <c r="W9">
+        <v>10000</v>
+      </c>
+      <c r="X9">
+        <v>20000</v>
+      </c>
+      <c r="Y9">
+        <v>20000</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2782</v>
+        <v>10611</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="C10">
-        <v>3206</v>
+        <v>2103</v>
       </c>
       <c r="D10">
-        <v>30604</v>
+        <v>20206</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I10">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1599,63 +1611,66 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="P10">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>169</v>
       </c>
       <c r="T10">
-        <v>285000</v>
+        <v>4000</v>
       </c>
       <c r="U10">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2870</v>
+        <v>7110</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="C11">
-        <v>3206</v>
+        <v>7109</v>
       </c>
       <c r="D11">
-        <v>30604</v>
+        <v>70909</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H11" t="s">
         <v>26</v>
       </c>
       <c r="I11">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1667,66 +1682,69 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="P11">
         <v>96</v>
       </c>
       <c r="Q11" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="T11">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2900</v>
+        <v>992</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>1108</v>
+        <v>3201</v>
       </c>
       <c r="D12">
-        <v>11211</v>
+        <v>30102</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
         <v>26</v>
       </c>
       <c r="I12">
-        <v>22</v>
+        <v>51</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1735,25 +1753,25 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>56</v>
+        <v>33</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
       </c>
       <c r="O12">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="P12">
-        <v>2</v>
-      </c>
-      <c r="R12" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="T12">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12">
-        <v>0</v>
+      <c r="V12" t="s">
+        <v>34</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -1767,31 +1785,31 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>3061</v>
+        <v>2585</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C13">
-        <v>4103</v>
+        <v>7206</v>
       </c>
       <c r="D13">
-        <v>40602</v>
+        <v>70811</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
         <v>26</v>
       </c>
       <c r="I13">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1803,16 +1821,16 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
       <c r="O13">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -1824,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="W13">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y13">
         <v>0</v>
@@ -1835,31 +1853,31 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>3111</v>
+        <v>2591</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C14">
-        <v>6201</v>
+        <v>7106</v>
       </c>
       <c r="D14">
-        <v>60303</v>
+        <v>70811</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
         <v>26</v>
       </c>
       <c r="I14">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1871,66 +1889,63 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="P14">
-        <v>2</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T14">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="U14">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="V14">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W14">
-        <v>19000</v>
+        <v>5000</v>
       </c>
       <c r="X14">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>3356</v>
+        <v>6967</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C15">
-        <v>5102</v>
+        <v>6106</v>
       </c>
       <c r="D15">
-        <v>50601</v>
+        <v>60806</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
         <v>63</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I15">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1942,42 +1957,66 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="N15">
-        <v>2</v>
-      </c>
-      <c r="R15" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>82</v>
+      </c>
+      <c r="P15">
+        <v>96</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>106</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>3656</v>
+        <v>9715</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="C16">
-        <v>3465</v>
+        <v>2104</v>
       </c>
       <c r="D16">
-        <v>30703</v>
+        <v>20214</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I16">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1989,22 +2028,19 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="N16">
         <v>2</v>
       </c>
       <c r="O16">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="P16">
-        <v>96</v>
-      </c>
-      <c r="R16" t="s">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="T16">
-        <v>150000</v>
+        <v>70000</v>
       </c>
       <c r="U16">
         <v>0</v>
@@ -2024,31 +2060,31 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>3683</v>
+        <v>9158</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="C17">
-        <v>1415</v>
+        <v>3204</v>
       </c>
       <c r="D17">
-        <v>11213</v>
+        <v>30512</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I17">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2057,37 +2093,22 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M17" t="s">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P17">
-        <v>2</v>
-      </c>
-      <c r="T17">
-        <v>800000</v>
+        <v>1</v>
       </c>
       <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
@@ -2163,31 +2184,31 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>3903</v>
+        <v>3061</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C19">
-        <v>2208</v>
+        <v>4103</v>
       </c>
       <c r="D19">
-        <v>20614</v>
+        <v>40602</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="H19" t="s">
         <v>26</v>
       </c>
       <c r="I19">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2199,37 +2220,31 @@
         <v>1</v>
       </c>
       <c r="M19" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="P19">
-        <v>96</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>77</v>
-      </c>
-      <c r="R19" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="X19">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -2237,22 +2252,22 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>3918</v>
+        <v>4509</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C20">
-        <v>7310</v>
+        <v>3205</v>
       </c>
       <c r="D20">
-        <v>70813</v>
+        <v>30601</v>
       </c>
       <c r="E20">
         <v>4</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
         <v>63</v>
@@ -2261,7 +2276,7 @@
         <v>26</v>
       </c>
       <c r="I20">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2270,69 +2285,66 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="N20">
         <v>1</v>
       </c>
       <c r="O20">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="P20">
-        <v>4</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="T20">
-        <v>30000</v>
+        <v>250000</v>
       </c>
       <c r="U20">
+        <v>60000</v>
+      </c>
+      <c r="V20">
+        <v>150000</v>
+      </c>
+      <c r="W20">
         <v>20000</v>
       </c>
-      <c r="V20">
-        <v>25000</v>
-      </c>
-      <c r="W20">
+      <c r="X20">
+        <v>15000</v>
+      </c>
+      <c r="Y20">
         <v>5000</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>3977</v>
+        <v>7464</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="C21">
-        <v>2208</v>
+        <v>5105</v>
       </c>
       <c r="D21">
-        <v>20614</v>
+        <v>50901</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
         <v>63</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I21">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2344,45 +2356,54 @@
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="P21">
-        <v>96</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="T21">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="U21">
+        <v>25000</v>
+      </c>
+      <c r="V21">
         <v>16000</v>
+      </c>
+      <c r="W21">
+        <v>6000</v>
+      </c>
+      <c r="X21">
+        <v>7000</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>4076</v>
+        <v>3977</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C22">
-        <v>2108</v>
+        <v>2208</v>
       </c>
       <c r="D22">
         <v>20614</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
         <v>63</v>
@@ -2391,7 +2412,7 @@
         <v>26</v>
       </c>
       <c r="I22">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2403,63 +2424,54 @@
         <v>1</v>
       </c>
       <c r="M22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N22">
         <v>1</v>
       </c>
       <c r="O22">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>84</v>
       </c>
       <c r="T22">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="U22">
-        <v>20000</v>
-      </c>
-      <c r="V22">
-        <v>20000</v>
-      </c>
-      <c r="W22">
-        <v>5000</v>
-      </c>
-      <c r="X22">
-        <v>5000</v>
-      </c>
-      <c r="Y22">
-        <v>30000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>4161</v>
+        <v>8786</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="C23">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="D23">
-        <v>11214</v>
+        <v>10207</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
         <v>63</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I23">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2471,28 +2483,31 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="N23">
         <v>1</v>
       </c>
       <c r="O23">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>156</v>
       </c>
       <c r="T23">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -2503,22 +2518,22 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4226</v>
+        <v>4161</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C24">
-        <v>3210</v>
+        <v>1109</v>
       </c>
       <c r="D24">
-        <v>30909</v>
+        <v>11214</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
         <v>63</v>
@@ -2527,7 +2542,7 @@
         <v>26</v>
       </c>
       <c r="I24">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2539,25 +2554,25 @@
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N24">
         <v>1</v>
       </c>
       <c r="O24">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T24">
-        <v>55000</v>
+        <v>50000</v>
       </c>
       <c r="U24">
+        <v>30000</v>
+      </c>
+      <c r="V24">
         <v>15000</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
       </c>
       <c r="W24">
         <v>5000</v>
@@ -2566,27 +2581,27 @@
         <v>0</v>
       </c>
       <c r="Y24">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>4243</v>
+        <v>4076</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C25">
-        <v>3210</v>
+        <v>2108</v>
       </c>
       <c r="D25">
-        <v>30909</v>
+        <v>20614</v>
       </c>
       <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
         <v>10</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
       </c>
       <c r="G25" t="s">
         <v>63</v>
@@ -2595,7 +2610,7 @@
         <v>26</v>
       </c>
       <c r="I25">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2607,63 +2622,63 @@
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N25">
         <v>1</v>
       </c>
       <c r="O25">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="P25">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>4509</v>
+        <v>2634</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="C26">
-        <v>3205</v>
+        <v>1109</v>
       </c>
       <c r="D26">
-        <v>30601</v>
+        <v>11214</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H26" t="s">
         <v>26</v>
       </c>
       <c r="I26">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2675,63 +2690,51 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="N26">
         <v>1</v>
       </c>
       <c r="O26">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>48</v>
       </c>
       <c r="T26">
-        <v>250000</v>
-      </c>
-      <c r="U26">
-        <v>60000</v>
-      </c>
-      <c r="V26">
-        <v>150000</v>
-      </c>
-      <c r="W26">
-        <v>20000</v>
-      </c>
-      <c r="X26">
         <v>15000</v>
-      </c>
-      <c r="Y26">
-        <v>5000</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4581</v>
+        <v>9655</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="C27">
-        <v>6202</v>
+        <v>1206</v>
       </c>
       <c r="D27">
-        <v>60404</v>
+        <v>11005</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F27">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I27">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2743,54 +2746,54 @@
         <v>1</v>
       </c>
       <c r="M27" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P27">
         <v>2</v>
       </c>
       <c r="T27">
-        <v>20000</v>
+        <v>560000</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y27">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4584</v>
+        <v>5998</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C28">
-        <v>6102</v>
+        <v>6204</v>
       </c>
       <c r="D28">
-        <v>60404</v>
+        <v>60608</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G28" t="s">
         <v>63</v>
@@ -2799,7 +2802,7 @@
         <v>27</v>
       </c>
       <c r="I28">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2807,26 +2810,20 @@
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
       <c r="M28" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P28">
-        <v>2</v>
-      </c>
-      <c r="R28" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="T28">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -2846,31 +2843,31 @@
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>4712</v>
+        <v>2341</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="C29">
-        <v>5103</v>
+        <v>1317</v>
       </c>
       <c r="D29">
-        <v>50609</v>
+        <v>11307</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I29">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2878,58 +2875,52 @@
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
       <c r="M29" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="N29">
         <v>1</v>
       </c>
       <c r="O29">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="P29">
-        <v>7</v>
-      </c>
-      <c r="T29" t="s">
-        <v>34</v>
-      </c>
-      <c r="U29" t="s">
-        <v>34</v>
-      </c>
-      <c r="V29" t="s">
-        <v>34</v>
-      </c>
-      <c r="W29" t="s">
-        <v>34</v>
-      </c>
-      <c r="X29" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>34</v>
+        <v>8</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>5146</v>
+        <v>5524</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C30">
-        <v>4201</v>
+        <v>3209</v>
       </c>
       <c r="D30">
-        <v>40204</v>
+        <v>30803</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
         <v>63</v>
@@ -2938,7 +2929,7 @@
         <v>27</v>
       </c>
       <c r="I30">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2947,61 +2938,70 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>2082</v>
       </c>
       <c r="M30" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="N30">
         <v>1</v>
       </c>
       <c r="O30">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="P30">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>112</v>
       </c>
       <c r="T30">
-        <v>1000000</v>
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>5150</v>
+        <v>3903</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C31">
-        <v>6204</v>
+        <v>2208</v>
       </c>
       <c r="D31">
-        <v>60608</v>
+        <v>20614</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G31" t="s">
         <v>63</v>
       </c>
       <c r="H31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31">
         <v>27</v>
       </c>
-      <c r="I31">
-        <v>64</v>
-      </c>
       <c r="J31">
         <v>1</v>
       </c>
@@ -3012,34 +3012,37 @@
         <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="P31">
         <v>96</v>
       </c>
       <c r="Q31" t="s">
-        <v>106</v>
+        <v>77</v>
+      </c>
+      <c r="R31" t="s">
+        <v>78</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Y31">
         <v>0</v>
@@ -3047,22 +3050,22 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5266</v>
+        <v>4584</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C32">
-        <v>7108</v>
+        <v>6102</v>
       </c>
       <c r="D32">
-        <v>70901</v>
+        <v>60404</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
         <v>63</v>
@@ -3071,7 +3074,7 @@
         <v>27</v>
       </c>
       <c r="I32">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3083,22 +3086,22 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32">
         <v>65</v>
       </c>
       <c r="P32">
-        <v>96</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>109</v>
+        <v>2</v>
+      </c>
+      <c r="R32" t="s">
+        <v>99</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -3118,28 +3121,28 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5517</v>
+        <v>10106</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="C33">
-        <v>3387</v>
+        <v>4206</v>
       </c>
       <c r="D33">
-        <v>30608</v>
+        <v>40803</v>
       </c>
       <c r="E33">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I33">
         <v>94</v>
@@ -3154,13 +3157,13 @@
         <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="P33">
         <v>96</v>
@@ -3169,19 +3172,19 @@
         <v>112</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Y33">
         <v>0</v>
@@ -3189,22 +3192,22 @@
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5524</v>
+        <v>5266</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C34">
-        <v>3209</v>
+        <v>7108</v>
       </c>
       <c r="D34">
-        <v>30803</v>
+        <v>70901</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
         <v>63</v>
@@ -3213,7 +3216,7 @@
         <v>27</v>
       </c>
       <c r="I34">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3222,22 +3225,22 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>2082</v>
+        <v>1</v>
       </c>
       <c r="M34" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="N34">
         <v>1</v>
       </c>
       <c r="O34">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="P34">
         <v>96</v>
       </c>
       <c r="Q34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -3260,31 +3263,31 @@
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>5892</v>
+        <v>10739</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="C35">
-        <v>2209</v>
+        <v>2204</v>
       </c>
       <c r="D35">
-        <v>20703</v>
+        <v>20214</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H35" t="s">
         <v>27</v>
       </c>
       <c r="I35">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3296,48 +3299,66 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="N35">
         <v>1</v>
       </c>
       <c r="O35">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>96</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>174</v>
       </c>
       <c r="T35">
-        <v>35000</v>
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5998</v>
+        <v>11029</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="C36">
-        <v>6204</v>
+        <v>2103</v>
       </c>
       <c r="D36">
-        <v>60608</v>
+        <v>20206</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G36" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H36" t="s">
         <v>27</v>
       </c>
       <c r="I36">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -3345,20 +3366,23 @@
       <c r="K36">
         <v>1</v>
       </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
       <c r="M36" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="N36">
         <v>1</v>
       </c>
       <c r="O36">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="P36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -3378,31 +3402,31 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>6013</v>
+        <v>7595</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C37">
-        <v>6204</v>
+        <v>5205</v>
       </c>
       <c r="D37">
-        <v>60608</v>
+        <v>50901</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G37" t="s">
         <v>63</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I37">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3411,66 +3435,57 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>142</v>
       </c>
       <c r="T37">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>96000</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>6671</v>
+        <v>10909</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="C38">
-        <v>4108</v>
+        <v>4205</v>
       </c>
       <c r="D38">
-        <v>41003</v>
+        <v>40704</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H38" t="s">
         <v>27</v>
       </c>
       <c r="I38">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -3482,28 +3497,22 @@
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="N38">
         <v>2</v>
       </c>
       <c r="O38">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="P38">
-        <v>96</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>124</v>
-      </c>
-      <c r="R38" t="s">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="T38">
-        <v>18000</v>
+        <v>250000</v>
       </c>
       <c r="U38">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -3515,27 +3524,27 @@
         <v>0</v>
       </c>
       <c r="Y38">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6967</v>
+        <v>5146</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C39">
-        <v>6106</v>
+        <v>4201</v>
       </c>
       <c r="D39">
-        <v>60806</v>
+        <v>40204</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
         <v>63</v>
@@ -3544,7 +3553,7 @@
         <v>27</v>
       </c>
       <c r="I39">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -3556,57 +3565,48 @@
         <v>1</v>
       </c>
       <c r="M39" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="N39">
         <v>1</v>
       </c>
       <c r="O39">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="P39">
-        <v>96</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39">
-        <v>0</v>
-      </c>
-      <c r="V39">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>7110</v>
+        <v>3656</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="C40">
-        <v>7109</v>
+        <v>3465</v>
       </c>
       <c r="D40">
-        <v>70909</v>
+        <v>30703</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F40">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G40" t="s">
         <v>63</v>
@@ -3615,7 +3615,7 @@
         <v>26</v>
       </c>
       <c r="I40">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -3627,57 +3627,57 @@
         <v>1</v>
       </c>
       <c r="M40" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="P40">
         <v>96</v>
       </c>
-      <c r="Q40" t="s">
-        <v>130</v>
+      <c r="R40" t="s">
+        <v>69</v>
       </c>
       <c r="T40">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="U40">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>7225</v>
+        <v>4712</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="C41">
-        <v>2101</v>
+        <v>5103</v>
       </c>
       <c r="D41">
-        <v>20110</v>
+        <v>50609</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
         <v>63</v>
@@ -3686,7 +3686,7 @@
         <v>27</v>
       </c>
       <c r="I41">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3698,63 +3698,63 @@
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="P41">
-        <v>2</v>
-      </c>
-      <c r="T41">
-        <v>1400000</v>
+        <v>7</v>
+      </c>
+      <c r="T41" t="s">
+        <v>34</v>
       </c>
       <c r="U41" t="s">
         <v>34</v>
       </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <v>0</v>
+      <c r="V41" t="s">
+        <v>34</v>
+      </c>
+      <c r="W41" t="s">
+        <v>34</v>
+      </c>
+      <c r="X41" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>7464</v>
+        <v>8508</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="C42">
-        <v>5105</v>
+        <v>2202</v>
       </c>
       <c r="D42">
-        <v>50901</v>
+        <v>20111</v>
       </c>
       <c r="E42">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H42" t="s">
         <v>27</v>
       </c>
       <c r="I42">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -3766,31 +3766,34 @@
         <v>1</v>
       </c>
       <c r="M42" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="N42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="P42">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>153</v>
       </c>
       <c r="T42">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -3798,31 +3801,31 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>7585</v>
+        <v>1302</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="C43">
-        <v>5205</v>
+        <v>3111</v>
       </c>
       <c r="D43">
-        <v>50901</v>
+        <v>31101</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F43">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I43">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -3834,54 +3837,54 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P43">
         <v>96</v>
       </c>
       <c r="Q43" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="T43">
-        <v>150000</v>
-      </c>
-      <c r="U43" t="s">
-        <v>34</v>
-      </c>
-      <c r="V43" t="s">
-        <v>34</v>
-      </c>
-      <c r="W43" t="s">
-        <v>34</v>
-      </c>
-      <c r="X43" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>40000</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>7595</v>
+        <v>11161</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="C44">
-        <v>5205</v>
+        <v>2208</v>
       </c>
       <c r="D44">
-        <v>50901</v>
+        <v>20614</v>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F44">
         <v>19</v>
@@ -3893,7 +3896,7 @@
         <v>27</v>
       </c>
       <c r="I44">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -3902,57 +3905,69 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="N44">
         <v>2</v>
       </c>
       <c r="O44">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="P44">
-        <v>96</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>140</v>
+        <v>7</v>
+      </c>
+      <c r="R44" t="s">
+        <v>184</v>
       </c>
       <c r="T44">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2450</v>
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>8047</v>
+        <v>2442</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="C45">
-        <v>3104</v>
+        <v>2310</v>
       </c>
       <c r="D45">
-        <v>30512</v>
+        <v>20612</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I45">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -3961,66 +3976,63 @@
         <v>1</v>
       </c>
       <c r="L45">
-        <v>2081</v>
+        <v>6</v>
       </c>
       <c r="M45" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="N45">
         <v>1</v>
       </c>
       <c r="O45">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="P45">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>42</v>
       </c>
       <c r="T45">
-        <v>50000</v>
-      </c>
-      <c r="U45">
-        <v>20000</v>
-      </c>
-      <c r="V45">
-        <v>80000</v>
+        <v>15000</v>
       </c>
       <c r="W45">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X45">
         <v>0</v>
       </c>
       <c r="Y45">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>8293</v>
+        <v>8464</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C46">
-        <v>7105</v>
+        <v>2102</v>
       </c>
       <c r="D46">
-        <v>70601</v>
+        <v>20111</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="H46" t="s">
         <v>27</v>
       </c>
       <c r="I46">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -4029,28 +4041,28 @@
         <v>1</v>
       </c>
       <c r="L46">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="N46">
         <v>2</v>
       </c>
       <c r="O46">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="P46">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R46" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="T46">
         <v>0</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -4067,31 +4079,31 @@
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>8464</v>
+        <v>7225</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C47">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="D47">
-        <v>20111</v>
+        <v>20110</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G47" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H47" t="s">
         <v>27</v>
       </c>
       <c r="I47">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -4103,25 +4115,22 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="N47">
         <v>2</v>
       </c>
       <c r="O47">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="P47">
         <v>2</v>
       </c>
-      <c r="R47" t="s">
-        <v>148</v>
-      </c>
       <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>1200000</v>
+        <v>1400000</v>
+      </c>
+      <c r="U47" t="s">
+        <v>34</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -4138,34 +4147,31 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>8508</v>
+        <v>2900</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="C48">
-        <v>2202</v>
+        <v>1108</v>
       </c>
       <c r="D48">
-        <v>20111</v>
+        <v>11211</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F48">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G48" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="H48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I48">
-        <v>24</v>
-      </c>
-      <c r="J48">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -4174,22 +4180,19 @@
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>150</v>
-      </c>
-      <c r="N48">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="P48">
-        <v>96</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>151</v>
+        <v>2</v>
+      </c>
+      <c r="R48" t="s">
+        <v>57</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -4209,31 +4212,31 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>8786</v>
+        <v>770</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="C49">
-        <v>1101</v>
+        <v>5104</v>
       </c>
       <c r="D49">
-        <v>10207</v>
+        <v>50703</v>
       </c>
       <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49">
         <v>7</v>
       </c>
-      <c r="F49">
-        <v>14</v>
-      </c>
       <c r="G49" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="H49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I49">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -4245,22 +4248,22 @@
         <v>1</v>
       </c>
       <c r="M49" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="N49">
         <v>1</v>
       </c>
       <c r="O49">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P49">
         <v>96</v>
       </c>
       <c r="Q49" t="s">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -4280,31 +4283,31 @@
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>9158</v>
+        <v>5892</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="C50">
-        <v>3204</v>
+        <v>2209</v>
       </c>
       <c r="D50">
-        <v>30512</v>
+        <v>20703</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F50">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H50" t="s">
         <v>27</v>
       </c>
       <c r="I50">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -4313,42 +4316,42 @@
         <v>1</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="N50">
         <v>1</v>
       </c>
       <c r="O50">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="P50">
-        <v>1</v>
-      </c>
-      <c r="U50">
-        <v>300000</v>
+        <v>4</v>
+      </c>
+      <c r="T50">
+        <v>35000</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>9655</v>
+        <v>10305</v>
       </c>
       <c r="B51" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C51">
-        <v>1206</v>
+        <v>4206</v>
       </c>
       <c r="D51">
-        <v>11005</v>
+        <v>40803</v>
       </c>
       <c r="E51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
         <v>117</v>
@@ -4357,7 +4360,7 @@
         <v>26</v>
       </c>
       <c r="I51">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -4369,63 +4372,48 @@
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N51">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="O51">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="P51">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="R51">
+        <v>3</v>
       </c>
       <c r="T51">
-        <v>560000</v>
-      </c>
-      <c r="U51">
-        <v>45000</v>
-      </c>
-      <c r="V51">
-        <v>4000</v>
-      </c>
-      <c r="W51">
-        <v>12000</v>
-      </c>
-      <c r="X51">
-        <v>10000</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>9715</v>
+        <v>6538</v>
       </c>
       <c r="B52" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="C52">
-        <v>2104</v>
+        <v>1201</v>
       </c>
       <c r="D52">
-        <v>20214</v>
+        <v>10207</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H52" t="s">
         <v>27</v>
       </c>
       <c r="I52">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4433,23 +4421,20 @@
       <c r="K52">
         <v>1</v>
       </c>
-      <c r="L52">
-        <v>1</v>
-      </c>
       <c r="M52" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="N52">
         <v>2</v>
       </c>
       <c r="O52">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="P52">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T52">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -4469,31 +4454,31 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>10106</v>
+        <v>7585</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="C53">
-        <v>4206</v>
+        <v>5205</v>
       </c>
       <c r="D53">
-        <v>40803</v>
+        <v>50901</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F53">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I53">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -4505,66 +4490,66 @@
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="P53">
         <v>96</v>
       </c>
       <c r="Q53" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="T53">
-        <v>10000</v>
-      </c>
-      <c r="U53">
-        <v>5000</v>
-      </c>
-      <c r="V53">
-        <v>12000</v>
-      </c>
-      <c r="W53">
-        <v>5000</v>
-      </c>
-      <c r="X53">
-        <v>3000</v>
-      </c>
-      <c r="Y53">
-        <v>0</v>
+        <v>150000</v>
+      </c>
+      <c r="U53" t="s">
+        <v>34</v>
+      </c>
+      <c r="V53" t="s">
+        <v>34</v>
+      </c>
+      <c r="W53" t="s">
+        <v>34</v>
+      </c>
+      <c r="X53" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>10305</v>
+        <v>3111</v>
       </c>
       <c r="B54" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="C54">
-        <v>4206</v>
+        <v>6201</v>
       </c>
       <c r="D54">
-        <v>40803</v>
+        <v>60303</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="H54" t="s">
         <v>26</v>
       </c>
       <c r="I54">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -4576,27 +4561,45 @@
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>164</v>
+        <v>62</v>
+      </c>
+      <c r="N54">
+        <v>2</v>
       </c>
       <c r="O54">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="P54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>400000</v>
+        <v>30000</v>
+      </c>
+      <c r="U54">
+        <v>20000</v>
+      </c>
+      <c r="V54">
+        <v>10000</v>
+      </c>
+      <c r="W54">
+        <v>19000</v>
+      </c>
+      <c r="X54">
+        <v>5000</v>
+      </c>
+      <c r="Y54">
+        <v>50000</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10611</v>
+        <v>10738</v>
       </c>
       <c r="B55" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C55">
         <v>2103</v>
@@ -4608,7 +4611,7 @@
         <v>3</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G55" t="s">
         <v>117</v>
@@ -4617,7 +4620,7 @@
         <v>27</v>
       </c>
       <c r="I55">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -4629,22 +4632,22 @@
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="N55">
         <v>2</v>
       </c>
       <c r="O55">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="P55">
         <v>96</v>
       </c>
-      <c r="Q55" t="s">
-        <v>167</v>
+      <c r="R55">
+        <v>96</v>
       </c>
       <c r="T55">
-        <v>4000</v>
+        <v>50000</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -4664,31 +4667,31 @@
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10738</v>
+        <v>4226</v>
       </c>
       <c r="B56" t="s">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="C56">
-        <v>2103</v>
+        <v>3210</v>
       </c>
       <c r="D56">
-        <v>20206</v>
+        <v>30909</v>
       </c>
       <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
         <v>3</v>
       </c>
-      <c r="F56">
-        <v>8</v>
-      </c>
       <c r="G56" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I56">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -4700,66 +4703,63 @@
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="P56">
-        <v>96</v>
-      </c>
-      <c r="R56">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="T56">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X56">
         <v>0</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10739</v>
+        <v>2870</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="C57">
-        <v>2204</v>
+        <v>3206</v>
       </c>
       <c r="D57">
-        <v>20214</v>
+        <v>30604</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F57">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="H57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I57">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -4771,22 +4771,22 @@
         <v>1</v>
       </c>
       <c r="M57" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="P57">
         <v>96</v>
       </c>
       <c r="Q57" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -4806,31 +4806,31 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10769</v>
+        <v>4243</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="C58">
-        <v>2103</v>
+        <v>3210</v>
       </c>
       <c r="D58">
-        <v>20206</v>
+        <v>30909</v>
       </c>
       <c r="E58">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F58">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G58" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I58">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -4842,22 +4842,19 @@
         <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O58">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="P58">
-        <v>2</v>
-      </c>
-      <c r="R58" t="s">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="T58">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -4877,31 +4874,31 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10909</v>
+        <v>8047</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C59">
-        <v>4205</v>
+        <v>3104</v>
       </c>
       <c r="D59">
-        <v>40704</v>
+        <v>30512</v>
       </c>
       <c r="E59">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H59" t="s">
         <v>27</v>
       </c>
       <c r="I59">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -4910,66 +4907,66 @@
         <v>1</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>2081</v>
       </c>
       <c r="M59" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T59">
-        <v>250000</v>
+        <v>50000</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>11029</v>
+        <v>5517</v>
       </c>
       <c r="B60" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="C60">
-        <v>2103</v>
+        <v>3387</v>
       </c>
       <c r="D60">
-        <v>20206</v>
+        <v>30608</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F60">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="H60" t="s">
         <v>27</v>
       </c>
       <c r="I60">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -4981,19 +4978,22 @@
         <v>1</v>
       </c>
       <c r="M60" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="N60">
         <v>1</v>
       </c>
       <c r="O60">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P60">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>112</v>
       </c>
       <c r="T60">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -5013,22 +5013,22 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>11161</v>
+        <v>8293</v>
       </c>
       <c r="B61" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C61">
-        <v>2208</v>
+        <v>7105</v>
       </c>
       <c r="D61">
-        <v>20614</v>
+        <v>70601</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G61" t="s">
         <v>63</v>
@@ -5037,7 +5037,7 @@
         <v>27</v>
       </c>
       <c r="I61">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -5046,22 +5046,22 @@
         <v>1</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M61" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="N61">
         <v>2</v>
       </c>
       <c r="O61">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="P61">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R61" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="T61">
         <v>0</v>
@@ -5079,13 +5079,84 @@
         <v>0</v>
       </c>
       <c r="Y61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>3918</v>
+      </c>
+      <c r="B62" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62">
+        <v>7310</v>
+      </c>
+      <c r="D62">
+        <v>70813</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+      <c r="F62">
+        <v>9</v>
+      </c>
+      <c r="G62" t="s">
+        <v>63</v>
+      </c>
+      <c r="H62" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62">
+        <v>72</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>80</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <v>95</v>
+      </c>
+      <c r="P62">
+        <v>4</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>81</v>
+      </c>
+      <c r="T62">
+        <v>30000</v>
+      </c>
+      <c r="U62">
+        <v>20000</v>
+      </c>
+      <c r="V62">
+        <v>25000</v>
+      </c>
+      <c r="W62">
+        <v>5000</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y61">
-    <sortCondition ref="A1:A61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y62">
+    <sortCondition ref="M1:M62"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6217A9B0-6ED1-454D-9148-8B78B7487611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8981DD32-B3BB-41CF-B22C-F3203735071F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="202">
   <si>
     <t>ID</t>
   </si>
@@ -586,6 +586,57 @@
   </si>
   <si>
     <t>96, RAMRO</t>
+  </si>
+  <si>
+    <t>5a56b014-dc70-4061-b579-f4a5705a2030</t>
+  </si>
+  <si>
+    <t>PUSHPA RAJ LOHANI</t>
+  </si>
+  <si>
+    <t>e1bad098-4e11-4564-8520-b293b907e1f8</t>
+  </si>
+  <si>
+    <t>RAM BAHADUR TAMANG</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DENGUE</t>
+  </si>
+  <si>
+    <t>c305a8bd-733c-4b30-9df9-09aee9e27a15</t>
+  </si>
+  <si>
+    <t>SHOBHA SUNUWAR</t>
+  </si>
+  <si>
+    <t>a2124962-4d70-4f9b-bc04-aeeddd2c560c</t>
+  </si>
+  <si>
+    <t>BINOD NEPALI PARIYAR</t>
+  </si>
+  <si>
+    <t>c44b384a-e2e4-4427-9c63-41ba75b152fd</t>
+  </si>
+  <si>
+    <t>DUKHINI DEVI CHAUDHARY</t>
+  </si>
+  <si>
+    <t>96, CANCER</t>
+  </si>
+  <si>
+    <t>366e0be3-df50-417c-a6ae-c278383edaa6</t>
+  </si>
+  <si>
+    <t>PURNA BAHADUR DUWAL</t>
+  </si>
+  <si>
+    <t>279e7337-4bb3-4954-9559-97bd14925fb9</t>
+  </si>
+  <si>
+    <t>TANK PRASHAD MAHATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BLOOD PRESSURE</t>
   </si>
 </sst>
 </file>
@@ -631,9 +682,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -938,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y62"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -5153,6 +5205,476 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>11382</v>
+      </c>
+      <c r="B63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63">
+        <v>3608</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>27</v>
+      </c>
+      <c r="G63" t="s">
+        <v>117</v>
+      </c>
+      <c r="H63" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63">
+        <v>94</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63" t="s">
+        <v>186</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <v>53</v>
+      </c>
+      <c r="P63">
+        <v>2</v>
+      </c>
+      <c r="T63">
+        <v>200000</v>
+      </c>
+      <c r="U63">
+        <v>50000</v>
+      </c>
+      <c r="V63">
+        <v>50000</v>
+      </c>
+      <c r="W63">
+        <v>20000</v>
+      </c>
+      <c r="X63">
+        <v>10000</v>
+      </c>
+      <c r="Y63">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>11336</v>
+      </c>
+      <c r="B64" t="s">
+        <v>187</v>
+      </c>
+      <c r="C64">
+        <v>3215</v>
+      </c>
+      <c r="D64">
+        <v>31304</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64" t="s">
+        <v>117</v>
+      </c>
+      <c r="H64" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64">
+        <v>53</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64" t="s">
+        <v>188</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <v>83</v>
+      </c>
+      <c r="P64">
+        <v>96</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>189</v>
+      </c>
+      <c r="T64">
+        <v>13000</v>
+      </c>
+      <c r="U64">
+        <v>600</v>
+      </c>
+      <c r="V64">
+        <v>10000</v>
+      </c>
+      <c r="W64">
+        <v>1600</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>11374</v>
+      </c>
+      <c r="B65" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65">
+        <v>3501</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>27</v>
+      </c>
+      <c r="G65" t="s">
+        <v>117</v>
+      </c>
+      <c r="H65" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65">
+        <v>91</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
+        <v>191</v>
+      </c>
+      <c r="N65">
+        <v>2</v>
+      </c>
+      <c r="O65">
+        <v>55</v>
+      </c>
+      <c r="P65">
+        <v>2</v>
+      </c>
+      <c r="T65">
+        <v>150000</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>11712</v>
+      </c>
+      <c r="B66" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66">
+        <v>3518</v>
+      </c>
+      <c r="D66">
+        <v>30610</v>
+      </c>
+      <c r="E66">
+        <v>7</v>
+      </c>
+      <c r="F66">
+        <v>57</v>
+      </c>
+      <c r="G66" t="s">
+        <v>117</v>
+      </c>
+      <c r="H66" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66">
+        <v>93</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66" t="s">
+        <v>193</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>26</v>
+      </c>
+      <c r="P66">
+        <v>2</v>
+      </c>
+      <c r="T66">
+        <v>122000</v>
+      </c>
+      <c r="U66">
+        <v>80000</v>
+      </c>
+      <c r="V66">
+        <v>17000</v>
+      </c>
+      <c r="W66">
+        <v>5000</v>
+      </c>
+      <c r="X66">
+        <v>20000</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>11880</v>
+      </c>
+      <c r="B67" t="s">
+        <v>194</v>
+      </c>
+      <c r="C67">
+        <v>3531</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>25</v>
+      </c>
+      <c r="G67" t="s">
+        <v>117</v>
+      </c>
+      <c r="H67" t="s">
+        <v>27</v>
+      </c>
+      <c r="I67">
+        <v>58</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67" t="s">
+        <v>195</v>
+      </c>
+      <c r="N67">
+        <v>2</v>
+      </c>
+      <c r="O67">
+        <v>62</v>
+      </c>
+      <c r="P67">
+        <v>2</v>
+      </c>
+      <c r="R67" t="s">
+        <v>196</v>
+      </c>
+      <c r="T67">
+        <v>527000</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>11588</v>
+      </c>
+      <c r="B68" t="s">
+        <v>197</v>
+      </c>
+      <c r="C68">
+        <v>3616</v>
+      </c>
+      <c r="D68">
+        <v>30703</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68">
+        <v>50</v>
+      </c>
+      <c r="G68" t="s">
+        <v>117</v>
+      </c>
+      <c r="H68" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68">
+        <v>94</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>198</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>78</v>
+      </c>
+      <c r="P68">
+        <v>2</v>
+      </c>
+      <c r="T68">
+        <v>200000</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>11903</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C69">
+        <v>4207</v>
+      </c>
+      <c r="D69">
+        <v>40806</v>
+      </c>
+      <c r="E69">
+        <v>14</v>
+      </c>
+      <c r="F69">
+        <v>36</v>
+      </c>
+      <c r="G69" t="s">
+        <v>117</v>
+      </c>
+      <c r="H69" t="s">
+        <v>27</v>
+      </c>
+      <c r="I69">
+        <v>26</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69" t="s">
+        <v>200</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69">
+        <v>64</v>
+      </c>
+      <c r="P69">
+        <v>96</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>201</v>
+      </c>
+      <c r="T69">
+        <v>50000</v>
+      </c>
+      <c r="U69">
+        <v>30000</v>
+      </c>
+      <c r="V69">
+        <v>20000</v>
+      </c>
+      <c r="W69">
+        <v>3000</v>
+      </c>
+      <c r="X69">
+        <v>10000</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y62">

--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-18-today\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-28-today (1)\2025-11-28-today\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8981DD32-B3BB-41CF-B22C-F3203735071F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2239B7-CCD2-4546-A676-DDFE1DA8D757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="212">
   <si>
     <t>ID</t>
   </si>
@@ -637,6 +637,36 @@
   </si>
   <si>
     <t xml:space="preserve"> BLOOD PRESSURE</t>
+  </si>
+  <si>
+    <t>2b6ba86c-24a8-439a-a8a6-e78c2eeeb559</t>
+  </si>
+  <si>
+    <t>MAN KUMARI BUDHATHOKI</t>
+  </si>
+  <si>
+    <t>cf72101d-d4ba-482a-b682-72c144f4c6a0</t>
+  </si>
+  <si>
+    <t>BUDDHI BAHADUR MARJAN</t>
+  </si>
+  <si>
+    <t>250729b1-5b8f-47cc-b66c-2e70048d7941</t>
+  </si>
+  <si>
+    <t>RATNA MAHARJAN</t>
+  </si>
+  <si>
+    <t>e63da22e-36b6-4445-ac42-b6455713cdd2</t>
+  </si>
+  <si>
+    <t>SUSUMAYA SARKI</t>
+  </si>
+  <si>
+    <t>UMERA PUGER BITNU BHAYEKO</t>
+  </si>
+  <si>
+    <t>KUNAI HAIN, 96</t>
   </si>
 </sst>
 </file>
@@ -990,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y69"/>
+  <dimension ref="A1:Y73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -5675,6 +5705,284 @@
         <v>0</v>
       </c>
     </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>12157</v>
+      </c>
+      <c r="B70" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70">
+        <v>2616</v>
+      </c>
+      <c r="D70">
+        <v>20502</v>
+      </c>
+      <c r="E70">
+        <v>11</v>
+      </c>
+      <c r="F70">
+        <v>55</v>
+      </c>
+      <c r="G70" t="s">
+        <v>117</v>
+      </c>
+      <c r="H70" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70">
+        <v>22</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
+        <v>203</v>
+      </c>
+      <c r="N70">
+        <v>2</v>
+      </c>
+      <c r="O70">
+        <v>82</v>
+      </c>
+      <c r="P70">
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <v>70000</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>13733</v>
+      </c>
+      <c r="B71" t="s">
+        <v>204</v>
+      </c>
+      <c r="C71">
+        <v>3549</v>
+      </c>
+      <c r="D71">
+        <v>30802</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71">
+        <v>30</v>
+      </c>
+      <c r="G71" t="s">
+        <v>117</v>
+      </c>
+      <c r="H71" t="s">
+        <v>27</v>
+      </c>
+      <c r="I71">
+        <v>55</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
+        <v>205</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71">
+        <v>78</v>
+      </c>
+      <c r="P71">
+        <v>2</v>
+      </c>
+      <c r="T71">
+        <v>50000</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>13735</v>
+      </c>
+      <c r="B72" t="s">
+        <v>206</v>
+      </c>
+      <c r="C72">
+        <v>3549</v>
+      </c>
+      <c r="D72">
+        <v>30802</v>
+      </c>
+      <c r="E72">
+        <v>14</v>
+      </c>
+      <c r="F72">
+        <v>31</v>
+      </c>
+      <c r="G72" t="s">
+        <v>117</v>
+      </c>
+      <c r="H72" t="s">
+        <v>27</v>
+      </c>
+      <c r="I72">
+        <v>55</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>207</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72">
+        <v>50</v>
+      </c>
+      <c r="P72">
+        <v>2</v>
+      </c>
+      <c r="T72">
+        <v>35000</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>13570</v>
+      </c>
+      <c r="B73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73">
+        <v>2600</v>
+      </c>
+      <c r="D73">
+        <v>20315</v>
+      </c>
+      <c r="E73">
+        <v>8</v>
+      </c>
+      <c r="F73">
+        <v>44</v>
+      </c>
+      <c r="G73" t="s">
+        <v>117</v>
+      </c>
+      <c r="H73" t="s">
+        <v>27</v>
+      </c>
+      <c r="I73">
+        <v>24</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
+        <v>209</v>
+      </c>
+      <c r="N73">
+        <v>2</v>
+      </c>
+      <c r="O73">
+        <v>77</v>
+      </c>
+      <c r="P73" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q73">
+        <v>96</v>
+      </c>
+      <c r="R73" t="s">
+        <v>211</v>
+      </c>
+      <c r="T73">
+        <v>150000</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y62">

--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-11-28-today (1)\2025-11-28-today\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-12-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2239B7-CCD2-4546-A676-DDFE1DA8D757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5C23F7-1C7D-4EC4-BE04-0C823AD8CC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="243">
   <si>
     <t>ID</t>
   </si>
@@ -123,7 +123,10 @@
     <t>SADHU SARAN CHAUDHARY</t>
   </si>
   <si>
-    <t xml:space="preserve"> PARALYZED</t>
+    <t>PARALYZED</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 96</t>
   </si>
   <si>
     <t>v2</t>
@@ -144,7 +147,7 @@
     <t>PUNEYA MATA LUITEL</t>
   </si>
   <si>
-    <t xml:space="preserve"> PRESSURE</t>
+    <t>PRESSURE</t>
   </si>
   <si>
     <t>fb8b22b0-dcd8-4961-b90a-3e3cb309036e</t>
@@ -159,7 +162,7 @@
     <t>RAM CHANDRA SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve"> BUDO VAYARA</t>
+    <t>BUDO VAYARA</t>
   </si>
   <si>
     <t>d799c7f8-d3bf-4c33-bb7f-1a94d23a48c5</t>
@@ -177,7 +180,7 @@
     <t>JIWAXKSHA LAL SAH</t>
   </si>
   <si>
-    <t xml:space="preserve"> UMER PUGER</t>
+    <t>UMER PUGER</t>
   </si>
   <si>
     <t>v3</t>
@@ -195,7 +198,7 @@
     <t>SUKMAIL TAMANG</t>
   </si>
   <si>
-    <t xml:space="preserve"> BODY SOLILING</t>
+    <t>BODY SOLILING</t>
   </si>
   <si>
     <t>0a6bb8d0-c5b0-4bb0-a9ca-9a084f3c97cd</t>
@@ -225,6 +228,9 @@
     <t>v5</t>
   </si>
   <si>
+    <t>02</t>
+  </si>
+  <si>
     <t>bc7381d5-b43c-49bb-b6bb-ac8d8b051795</t>
   </si>
   <si>
@@ -240,7 +246,7 @@
     <t>POTA KUMARI KC</t>
   </si>
   <si>
-    <t>96, UMER PUGERA MRITYU VAYEKO</t>
+    <t>UMER PUGERA MRITYU VAYEKO, 96</t>
   </si>
   <si>
     <t>08a5ccdc-b3eb-442f-8158-978514f1c728</t>
@@ -255,7 +261,10 @@
     <t>DILIP DAHAL</t>
   </si>
   <si>
-    <t xml:space="preserve"> MIRGAULA KO KARNA</t>
+    <t>MIRGAULA KO KARNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2</t>
   </si>
   <si>
     <t>c0ed52ee-b5b1-42d2-978e-4b67f0862993</t>
@@ -264,7 +273,7 @@
     <t>LAXMI GUPTA</t>
   </si>
   <si>
-    <t xml:space="preserve"> HIP MA GHAU</t>
+    <t>HIP MA GHAU</t>
   </si>
   <si>
     <t>HIP MA GHAU VAYERA ACHANAK 1 WEEK MA MRITUBVAYO</t>
@@ -276,7 +285,10 @@
     <t>YAGYA RAJ JOSHI</t>
   </si>
   <si>
-    <t xml:space="preserve"> GHAR MA SAMANYA LADNU BHAYERA ANI HOSPITALIZED BHAYERA UHA KO NIDHAN BHAKO</t>
+    <t>GHAR MA SAMANYA LADNU BHAYERA ANI HOSPITALIZED BHAYERA UHA KO NIDHAN BHAKO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4</t>
   </si>
   <si>
     <t>f89adf4d-2a40-4bcd-8d8c-f1e3a001606f</t>
@@ -285,7 +297,7 @@
     <t>JALIL ANSARI</t>
   </si>
   <si>
-    <t xml:space="preserve"> DIMAG KO NASA FATERA</t>
+    <t>DIMAG KO NASA FATERA</t>
   </si>
   <si>
     <t>f5f844d6-f66e-4928-ac5b-b54e1fb0a9ff</t>
@@ -330,7 +342,7 @@
     <t>LILA DEVI UPADHYAY</t>
   </si>
   <si>
-    <t>96, ULCER</t>
+    <t>ULCER, 96</t>
   </si>
   <si>
     <t>3222b7cd-8688-4a88-b14f-13ada3f3fe69</t>
@@ -351,7 +363,7 @@
     <t>BAM BAHADUR CHAND</t>
   </si>
   <si>
-    <t xml:space="preserve"> AGE VAYERA</t>
+    <t>AGE VAYERA</t>
   </si>
   <si>
     <t>6b0815bf-0beb-4f0c-af76-df8729e84782</t>
@@ -360,7 +372,7 @@
     <t>MOHAN CHAUDHARY</t>
   </si>
   <si>
-    <t xml:space="preserve"> HEART ATTACK</t>
+    <t>HEART ATTACK</t>
   </si>
   <si>
     <t>8f626752-3c23-4680-860c-c03f2c5d9d5a</t>
@@ -378,6 +390,9 @@
     <t>LATAKANCHA TAMANG</t>
   </si>
   <si>
+    <t>OLD AGE</t>
+  </si>
+  <si>
     <t>328f772d-6811-4ee0-921f-af40f1094ba2</t>
   </si>
   <si>
@@ -411,10 +426,10 @@
     <t>AMBIKA SHARMA</t>
   </si>
   <si>
-    <t xml:space="preserve"> OLD AGE MULTI ORGAN FAIL</t>
-  </si>
-  <si>
-    <t>96, BUDO</t>
+    <t>OLD AGE MULTI ORGAN FAIL</t>
+  </si>
+  <si>
+    <t>BUDO, 96</t>
   </si>
   <si>
     <t>a29f713a-3813-4445-91e1-40fb4200a75e</t>
@@ -429,7 +444,7 @@
     <t>DEV BADHUR CHETTRI</t>
   </si>
   <si>
-    <t xml:space="preserve"> KIDDNI FAIL</t>
+    <t>KIDDNI FAIL</t>
   </si>
   <si>
     <t>95f113cf-7836-4fe9-9dd0-a519ade122f4</t>
@@ -450,7 +465,7 @@
     <t>SHOVAKHAR PANDEY</t>
   </si>
   <si>
-    <t xml:space="preserve"> INFECTION ON HAND</t>
+    <t>INFECTION ON HAND</t>
   </si>
   <si>
     <t>df18ff3e-5104-44a1-9b6f-676cdfe51bde</t>
@@ -459,7 +474,7 @@
     <t>PARBATI DEVI JAISI</t>
   </si>
   <si>
-    <t xml:space="preserve"> LADAKO</t>
+    <t>LADAKO</t>
   </si>
   <si>
     <t>0e9c3a0f-140b-4ca4-a852-28413aa0f81b</t>
@@ -474,7 +489,7 @@
     <t>TULSI DEVI KHADKA</t>
   </si>
   <si>
-    <t>96, UMER LAGERA DEATH VAYEKO</t>
+    <t>UMER LAGERA DEATH VAYEKO, 96</t>
   </si>
   <si>
     <t>d4fc662a-44a3-427b-946a-3a57bf25241d</t>
@@ -483,7 +498,7 @@
     <t>RAM KUMARI RAM</t>
   </si>
   <si>
-    <t>96, BREAST CANCER</t>
+    <t>BREAST CANCER, 96</t>
   </si>
   <si>
     <t>37eef006-aa9e-4b5b-b505-32689e51509c</t>
@@ -492,7 +507,7 @@
     <t>PRINSH PASAWAN</t>
   </si>
   <si>
-    <t xml:space="preserve"> THAHA NA VAYEKO</t>
+    <t>THAHA NA VAYEKO</t>
   </si>
   <si>
     <t>f50d8bbc-01ac-4dbe-abea-55675e75360f</t>
@@ -501,7 +516,7 @@
     <t>JHALAK BAHADUR THAPA</t>
   </si>
   <si>
-    <t xml:space="preserve"> BRIDHABASTHA</t>
+    <t>BRIDHABASTHA</t>
   </si>
   <si>
     <t>74a648d9-57c7-486b-a14b-aa2e14da4348</t>
@@ -540,7 +555,7 @@
     <t>DARBI DEVI BADHAI</t>
   </si>
   <si>
-    <t xml:space="preserve"> BUDO VAYE RA</t>
+    <t>BUDO VAYE RA</t>
   </si>
   <si>
     <t>3505e841-fc76-4266-9079-d7513db81159</t>
@@ -555,7 +570,7 @@
     <t>NAINI YADAV</t>
   </si>
   <si>
-    <t xml:space="preserve"> UMER PUGER BITNU  VAYEKO</t>
+    <t>UMER PUGER BITNU  VAYEKO</t>
   </si>
   <si>
     <t>3d772a18-6f5f-4e98-b19e-f227039c1fc0</t>
@@ -585,7 +600,22 @@
     <t>RABITA PATEL</t>
   </si>
   <si>
-    <t>96, RAMRO</t>
+    <t>RAMRO, 96</t>
+  </si>
+  <si>
+    <t>e1bad098-4e11-4564-8520-b293b907e1f8</t>
+  </si>
+  <si>
+    <t>RAM BAHADUR TAMANG</t>
+  </si>
+  <si>
+    <t>DENGUE</t>
+  </si>
+  <si>
+    <t>c305a8bd-733c-4b30-9df9-09aee9e27a15</t>
+  </si>
+  <si>
+    <t>SHOBHA SUNUWAR</t>
   </si>
   <si>
     <t>5a56b014-dc70-4061-b579-f4a5705a2030</t>
@@ -594,19 +624,19 @@
     <t>PUSHPA RAJ LOHANI</t>
   </si>
   <si>
-    <t>e1bad098-4e11-4564-8520-b293b907e1f8</t>
-  </si>
-  <si>
-    <t>RAM BAHADUR TAMANG</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DENGUE</t>
-  </si>
-  <si>
-    <t>c305a8bd-733c-4b30-9df9-09aee9e27a15</t>
-  </si>
-  <si>
-    <t>SHOBHA SUNUWAR</t>
+    <t>4fb10f65-0215-4146-97db-d2ed57921e64</t>
+  </si>
+  <si>
+    <t>LAT NARAYAN YADAV</t>
+  </si>
+  <si>
+    <t>UMER PUGERA</t>
+  </si>
+  <si>
+    <t>366e0be3-df50-417c-a6ae-c278383edaa6</t>
+  </si>
+  <si>
+    <t>PURNA BAHADUR DUWAL</t>
   </si>
   <si>
     <t>a2124962-4d70-4f9b-bc04-aeeddd2c560c</t>
@@ -621,13 +651,7 @@
     <t>DUKHINI DEVI CHAUDHARY</t>
   </si>
   <si>
-    <t>96, CANCER</t>
-  </si>
-  <si>
-    <t>366e0be3-df50-417c-a6ae-c278383edaa6</t>
-  </si>
-  <si>
-    <t>PURNA BAHADUR DUWAL</t>
+    <t>CANCER, 96</t>
   </si>
   <si>
     <t>279e7337-4bb3-4954-9559-97bd14925fb9</t>
@@ -636,7 +660,28 @@
     <t>TANK PRASHAD MAHATO</t>
   </si>
   <si>
-    <t xml:space="preserve"> BLOOD PRESSURE</t>
+    <t>BLOOD PRESSURE</t>
+  </si>
+  <si>
+    <t>7d3c61a4-54ef-475e-abda-c9f520b1b2c6</t>
+  </si>
+  <si>
+    <t>TEJ BAHADUR BISTA</t>
+  </si>
+  <si>
+    <t>f6a69017-1366-4a34-b140-5de452b27bb6</t>
+  </si>
+  <si>
+    <t>SHARAD MAHATO</t>
+  </si>
+  <si>
+    <t>ac98cfb9-b3b1-4957-9256-c67c2f936779</t>
+  </si>
+  <si>
+    <t>DIL KUMARI THARU</t>
+  </si>
+  <si>
+    <t>SAMANYA, 96</t>
   </si>
   <si>
     <t>2b6ba86c-24a8-439a-a8a6-e78c2eeeb559</t>
@@ -645,6 +690,33 @@
     <t>MAN KUMARI BUDHATHOKI</t>
   </si>
   <si>
+    <t>486eecfe-f032-44c1-a3cc-4561fadec8f6</t>
+  </si>
+  <si>
+    <t>SASHU</t>
+  </si>
+  <si>
+    <t>65cb8dac-b37e-4ead-a588-b69c9f31f825</t>
+  </si>
+  <si>
+    <t>MITHILESH THAKUR</t>
+  </si>
+  <si>
+    <t>HEART ATECT</t>
+  </si>
+  <si>
+    <t>e63da22e-36b6-4445-ac42-b6455713cdd2</t>
+  </si>
+  <si>
+    <t>SUSUMAYA SARKI</t>
+  </si>
+  <si>
+    <t>UMERA PUGER BITNU BHAYEKO</t>
+  </si>
+  <si>
+    <t>KUNAI HAIN, 96</t>
+  </si>
+  <si>
     <t>cf72101d-d4ba-482a-b682-72c144f4c6a0</t>
   </si>
   <si>
@@ -657,16 +729,37 @@
     <t>RATNA MAHARJAN</t>
   </si>
   <si>
-    <t>e63da22e-36b6-4445-ac42-b6455713cdd2</t>
-  </si>
-  <si>
-    <t>SUSUMAYA SARKI</t>
-  </si>
-  <si>
-    <t>UMERA PUGER BITNU BHAYEKO</t>
-  </si>
-  <si>
-    <t>KUNAI HAIN, 96</t>
+    <t>ba1cb7c9-949b-4e5f-913f-761518313453</t>
+  </si>
+  <si>
+    <t>SAROJ MARASAINI</t>
+  </si>
+  <si>
+    <t>4dc99ec6-8a39-4c97-91f5-1b2b24d7dc79</t>
+  </si>
+  <si>
+    <t>KRISHNA PSD UPDHYAYA</t>
+  </si>
+  <si>
+    <t>31b18d94-928c-4c88-9331-a57860a54c73</t>
+  </si>
+  <si>
+    <t>TIL BAHADUR GURUNG</t>
+  </si>
+  <si>
+    <t>b3468dbf-8b11-48e3-91a8-64e5ade22404</t>
+  </si>
+  <si>
+    <t>JITLAL MAHARJAN</t>
+  </si>
+  <si>
+    <t>6b8149cc-8b7a-4a19-8e32-133d5bc61744</t>
+  </si>
+  <si>
+    <t>MAN KUMARI KHADKA</t>
+  </si>
+  <si>
+    <t>NORMAL</t>
   </si>
 </sst>
 </file>
@@ -712,10 +805,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1020,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1033,8 +1125,9 @@
     <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="88.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="56.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -1125,7 +1218,7 @@
         <v>6671</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C2">
         <v>4108</v>
@@ -1140,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H2" t="s">
         <v>27</v>
@@ -1158,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -1166,14 +1259,14 @@
       <c r="O2">
         <v>98</v>
       </c>
-      <c r="P2">
-        <v>96</v>
+      <c r="P2" t="s">
+        <v>131</v>
       </c>
       <c r="Q2" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="R2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="T2">
         <v>18000</v>
@@ -1199,7 +1292,7 @@
         <v>5150</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>6204</v>
@@ -1214,7 +1307,7 @@
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H3" t="s">
         <v>27</v>
@@ -1232,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -1240,11 +1333,11 @@
       <c r="O3">
         <v>82</v>
       </c>
-      <c r="P3">
-        <v>96</v>
+      <c r="P3" t="s">
+        <v>110</v>
       </c>
       <c r="Q3" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -1270,7 +1363,7 @@
         <v>3683</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>1415</v>
@@ -1285,7 +1378,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H4" t="s">
         <v>26</v>
@@ -1303,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N4">
         <v>2</v>
@@ -1338,7 +1431,7 @@
         <v>10769</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C5">
         <v>2103</v>
@@ -1353,7 +1446,7 @@
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H5" t="s">
         <v>27</v>
@@ -1371,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -1383,7 +1476,7 @@
         <v>2</v>
       </c>
       <c r="R5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="T5">
         <v>50000</v>
@@ -1406,31 +1499,31 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4581</v>
+        <v>11712</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="C6">
-        <v>6202</v>
+        <v>3518</v>
       </c>
       <c r="D6">
-        <v>60404</v>
+        <v>30610</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H6" t="s">
         <v>27</v>
       </c>
       <c r="I6">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1442,63 +1535,63 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>96</v>
+        <v>203</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
       <c r="O6">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="P6">
         <v>2</v>
       </c>
       <c r="T6">
+        <v>122000</v>
+      </c>
+      <c r="U6">
+        <v>80000</v>
+      </c>
+      <c r="V6">
+        <v>17000</v>
+      </c>
+      <c r="W6">
+        <v>5000</v>
+      </c>
+      <c r="X6">
         <v>20000</v>
       </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
       <c r="Y6">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3356</v>
+        <v>13733</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>228</v>
       </c>
       <c r="C7">
-        <v>5102</v>
+        <v>3549</v>
       </c>
       <c r="D7">
-        <v>50601</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
+        <v>30802</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1510,42 +1603,63 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>65</v>
+        <v>229</v>
       </c>
       <c r="N7">
-        <v>2</v>
-      </c>
-      <c r="R7" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>78</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>50000</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>6013</v>
+        <v>4581</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="C8">
-        <v>6204</v>
+        <v>6202</v>
       </c>
       <c r="D8">
-        <v>60608</v>
+        <v>60404</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1557,13 +1671,13 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
       <c r="O8">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P8">
         <v>2</v>
@@ -1584,36 +1698,36 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>96000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2782</v>
+        <v>3356</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>3206</v>
+        <v>5102</v>
       </c>
       <c r="D9">
-        <v>30604</v>
+        <v>50601</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="H9" t="s">
         <v>26</v>
       </c>
       <c r="I9">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1625,63 +1739,42 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>84</v>
-      </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
-      <c r="T9">
-        <v>285000</v>
-      </c>
-      <c r="U9">
-        <v>115000</v>
-      </c>
-      <c r="V9">
-        <v>75000</v>
-      </c>
-      <c r="W9">
-        <v>10000</v>
-      </c>
-      <c r="X9">
-        <v>20000</v>
-      </c>
-      <c r="Y9">
-        <v>20000</v>
+        <v>2</v>
+      </c>
+      <c r="R9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>10611</v>
+        <v>6013</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="C10">
-        <v>2103</v>
+        <v>6204</v>
       </c>
       <c r="D10">
-        <v>20206</v>
+        <v>60608</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I10">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1693,22 +1786,19 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="P10">
-        <v>96</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
       <c r="T10">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1723,36 +1813,36 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>7110</v>
+        <v>2782</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="C11">
-        <v>7109</v>
+        <v>3206</v>
       </c>
       <c r="D11">
-        <v>70909</v>
+        <v>30604</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F11">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
         <v>26</v>
       </c>
       <c r="I11">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1764,96 +1854,96 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="O11">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="P11">
-        <v>96</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="T11">
-        <v>200000</v>
+        <v>285000</v>
       </c>
       <c r="U11">
+        <v>115000</v>
+      </c>
+      <c r="V11">
+        <v>75000</v>
+      </c>
+      <c r="W11">
+        <v>10000</v>
+      </c>
+      <c r="X11">
         <v>20000</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>15000</v>
-      </c>
-      <c r="X11">
-        <v>12000</v>
-      </c>
       <c r="Y11">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>992</v>
+        <v>10611</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="C12">
-        <v>3201</v>
+        <v>2103</v>
       </c>
       <c r="D12">
-        <v>30102</v>
+        <v>20206</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12">
+        <v>22</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>173</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>110</v>
+      </c>
+      <c r="P12" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q12" t="s">
         <v>31</v>
       </c>
-      <c r="H12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12">
-        <v>51</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>32</v>
-      </c>
-      <c r="P12">
-        <v>4</v>
-      </c>
       <c r="T12">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" t="s">
-        <v>34</v>
+      <c r="V12">
+        <v>0</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -1867,25 +1957,25 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2585</v>
+        <v>7110</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C13">
-        <v>7206</v>
+        <v>7109</v>
       </c>
       <c r="D13">
-        <v>70811</v>
+        <v>70909</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
         <v>26</v>
@@ -1903,63 +1993,66 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
       <c r="O13">
-        <v>80</v>
-      </c>
-      <c r="P13">
-        <v>7</v>
+        <v>46</v>
+      </c>
+      <c r="P13" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>31</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2591</v>
+        <v>992</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C14">
-        <v>7106</v>
+        <v>3201</v>
       </c>
       <c r="D14">
-        <v>70811</v>
+        <v>30102</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
         <v>26</v>
       </c>
       <c r="I14">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1971,28 +2064,28 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="O14">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="P14">
         <v>4</v>
       </c>
       <c r="T14">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>10000</v>
-      </c>
-      <c r="V14">
-        <v>15000</v>
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>35</v>
       </c>
       <c r="W14">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X14">
         <v>0</v>
@@ -2003,31 +2096,31 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>6967</v>
+        <v>2585</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="C15">
-        <v>6106</v>
+        <v>7206</v>
       </c>
       <c r="D15">
-        <v>60806</v>
+        <v>70811</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I15">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2039,19 +2132,16 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P15">
-        <v>96</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -2074,64 +2164,64 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9715</v>
+        <v>2591</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="C16">
-        <v>2104</v>
+        <v>7106</v>
       </c>
       <c r="D16">
-        <v>20214</v>
+        <v>70811</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16">
+        <v>74</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>45</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>54</v>
+      </c>
+      <c r="P16">
         <v>4</v>
       </c>
-      <c r="G16" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16">
-        <v>22</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16" t="s">
-        <v>162</v>
-      </c>
-      <c r="N16">
-        <v>2</v>
-      </c>
-      <c r="O16">
-        <v>70</v>
-      </c>
-      <c r="P16">
-        <v>2</v>
-      </c>
       <c r="T16">
-        <v>70000</v>
+        <v>20000</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X16">
         <v>0</v>
@@ -2142,31 +2232,31 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9158</v>
+        <v>6967</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="C17">
-        <v>3204</v>
+        <v>6106</v>
       </c>
       <c r="D17">
-        <v>30512</v>
+        <v>60806</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
         <v>27</v>
       </c>
       <c r="I17">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2175,51 +2265,69 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
       <c r="O17">
-        <v>69</v>
-      </c>
-      <c r="P17">
-        <v>1</v>
+        <v>82</v>
+      </c>
+      <c r="P17" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>31</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>300000</v>
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>3862</v>
+        <v>9715</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="C18">
-        <v>1315</v>
+        <v>2104</v>
       </c>
       <c r="D18">
-        <v>11213</v>
+        <v>20214</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I18">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2231,34 +2339,31 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="P18">
         <v>2</v>
       </c>
-      <c r="Q18" t="s">
-        <v>74</v>
-      </c>
       <c r="T18">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="U18">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -2266,31 +2371,31 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>3061</v>
+        <v>9158</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="C19">
-        <v>4103</v>
+        <v>3204</v>
       </c>
       <c r="D19">
-        <v>40602</v>
+        <v>30512</v>
       </c>
       <c r="E19">
         <v>4</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I19">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2299,134 +2404,122 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="N19">
         <v>1</v>
       </c>
       <c r="O19">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P19">
         <v>1</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>4000</v>
-      </c>
-      <c r="X19">
-        <v>2000</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>4509</v>
+        <v>11990</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="C20">
-        <v>3205</v>
+        <v>4107</v>
       </c>
       <c r="D20">
-        <v>30601</v>
+        <v>40806</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20">
+        <v>51</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>215</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20">
         <v>26</v>
       </c>
-      <c r="I20">
-        <v>94</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>79</v>
-      </c>
       <c r="P20">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="R20" t="s">
+        <v>216</v>
       </c>
       <c r="T20">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>7464</v>
+        <v>3862</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="C21">
-        <v>5105</v>
+        <v>1315</v>
       </c>
       <c r="D21">
-        <v>50901</v>
+        <v>11213</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I21">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2438,28 +2531,31 @@
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21">
-        <v>71</v>
-      </c>
-      <c r="P21">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="P21" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>77</v>
       </c>
       <c r="T21">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="U21">
-        <v>25000</v>
+        <v>200000</v>
       </c>
       <c r="V21">
-        <v>16000</v>
+        <v>120000</v>
       </c>
       <c r="W21">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="X21">
         <v>7000</v>
@@ -2470,31 +2566,28 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3977</v>
+        <v>11880</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="C22">
-        <v>2208</v>
-      </c>
-      <c r="D22">
-        <v>20614</v>
+        <v>3531</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I22">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2506,54 +2599,60 @@
         <v>1</v>
       </c>
       <c r="M22" t="s">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="P22">
-        <v>96</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>84</v>
+        <v>2</v>
+      </c>
+      <c r="R22" t="s">
+        <v>206</v>
       </c>
       <c r="T22">
-        <v>40000</v>
-      </c>
-      <c r="U22">
-        <v>16000</v>
+        <v>527000</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>8786</v>
+        <v>3061</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="C23">
-        <v>1101</v>
+        <v>4103</v>
       </c>
       <c r="D23">
-        <v>10207</v>
+        <v>40602</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I23">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2565,19 +2664,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="N23">
         <v>1</v>
       </c>
       <c r="O23">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P23">
-        <v>96</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -2589,10 +2685,10 @@
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y23">
         <v>0</v>
@@ -2600,31 +2696,31 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4161</v>
+        <v>4509</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C24">
-        <v>1109</v>
+        <v>3205</v>
       </c>
       <c r="D24">
-        <v>11214</v>
+        <v>30601</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" t="s">
         <v>26</v>
       </c>
       <c r="I24">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2636,63 +2732,63 @@
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="N24">
         <v>1</v>
       </c>
       <c r="O24">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="P24">
         <v>2</v>
       </c>
       <c r="T24">
-        <v>50000</v>
+        <v>250000</v>
       </c>
       <c r="U24">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="V24">
+        <v>150000</v>
+      </c>
+      <c r="W24">
+        <v>20000</v>
+      </c>
+      <c r="X24">
         <v>15000</v>
       </c>
-      <c r="W24">
+      <c r="Y24">
         <v>5000</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>4076</v>
+        <v>7464</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="C25">
-        <v>2108</v>
+        <v>5105</v>
       </c>
       <c r="D25">
-        <v>20614</v>
+        <v>50901</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I25">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2704,63 +2800,63 @@
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="P25">
         <v>2</v>
       </c>
       <c r="T25">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="U25">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="V25">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="W25">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="X25">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="Y25">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2634</v>
+        <v>3977</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="C26">
-        <v>1109</v>
+        <v>2208</v>
       </c>
       <c r="D26">
-        <v>11214</v>
+        <v>20614</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="H26" t="s">
         <v>26</v>
       </c>
       <c r="I26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2772,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -2780,40 +2876,43 @@
       <c r="O26">
         <v>80</v>
       </c>
-      <c r="P26">
-        <v>96</v>
+      <c r="P26" t="s">
+        <v>88</v>
       </c>
       <c r="Q26" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="T26">
-        <v>15000</v>
+        <v>40000</v>
+      </c>
+      <c r="U26">
+        <v>16000</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>9655</v>
+        <v>8786</v>
       </c>
       <c r="B27" t="s">
         <v>159</v>
       </c>
       <c r="C27">
-        <v>1206</v>
+        <v>1101</v>
       </c>
       <c r="D27">
-        <v>11005</v>
+        <v>10207</v>
       </c>
       <c r="E27">
         <v>7</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27">
         <v>11</v>
@@ -2831,28 +2930,31 @@
         <v>160</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27">
-        <v>65</v>
-      </c>
-      <c r="P27">
-        <v>2</v>
+        <v>73</v>
+      </c>
+      <c r="P27" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>31</v>
       </c>
       <c r="T27">
-        <v>560000</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y27">
         <v>0</v>
@@ -2860,31 +2962,31 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>5998</v>
+        <v>4161</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="C28">
-        <v>6204</v>
+        <v>1109</v>
       </c>
       <c r="D28">
-        <v>60608</v>
+        <v>11214</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2892,29 +2994,32 @@
       <c r="K28">
         <v>1</v>
       </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
       <c r="M28" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="N28">
         <v>1</v>
       </c>
       <c r="O28">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="P28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X28">
         <v>0</v>
@@ -2925,31 +3030,31 @@
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2341</v>
+        <v>4076</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C29">
-        <v>1317</v>
+        <v>2108</v>
       </c>
       <c r="D29">
-        <v>11307</v>
+        <v>20614</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="H29" t="s">
         <v>26</v>
       </c>
       <c r="I29">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2957,61 +3062,67 @@
       <c r="K29">
         <v>1</v>
       </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
       <c r="M29" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="N29">
         <v>1</v>
       </c>
       <c r="O29">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="P29">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>5000</v>
+      </c>
+      <c r="Y29">
+        <v>30000</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>5524</v>
+        <v>14305</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>238</v>
       </c>
       <c r="C30">
-        <v>3209</v>
+        <v>3481</v>
       </c>
       <c r="D30">
-        <v>30803</v>
+        <v>30802</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="G30" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H30" t="s">
         <v>27</v>
       </c>
       <c r="I30">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3020,25 +3131,22 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>2082</v>
+        <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="N30">
         <v>1</v>
       </c>
       <c r="O30">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P30">
-        <v>96</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -3058,31 +3166,31 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>3903</v>
+        <v>2634</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C31">
-        <v>2208</v>
+        <v>1109</v>
       </c>
       <c r="D31">
-        <v>20614</v>
+        <v>11214</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="H31" t="s">
         <v>26</v>
       </c>
       <c r="I31">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3094,69 +3202,51 @@
         <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31">
-        <v>50</v>
-      </c>
-      <c r="P31">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="P31" t="s">
+        <v>49</v>
       </c>
       <c r="Q31" t="s">
-        <v>77</v>
-      </c>
-      <c r="R31" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="T31">
-        <v>300000</v>
-      </c>
-      <c r="U31">
-        <v>200000</v>
-      </c>
-      <c r="V31">
-        <v>50000</v>
-      </c>
-      <c r="W31">
-        <v>20000</v>
-      </c>
-      <c r="X31">
-        <v>30000</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>4584</v>
+        <v>9655</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="C32">
-        <v>6102</v>
+        <v>1206</v>
       </c>
       <c r="D32">
-        <v>60404</v>
+        <v>11005</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I32">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3168,7 +3258,7 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -3179,23 +3269,20 @@
       <c r="P32">
         <v>2</v>
       </c>
-      <c r="R32" t="s">
-        <v>99</v>
-      </c>
       <c r="T32">
-        <v>22000</v>
+        <v>560000</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y32">
         <v>0</v>
@@ -3203,31 +3290,31 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>10106</v>
+        <v>5998</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="C33">
-        <v>4206</v>
+        <v>6204</v>
       </c>
       <c r="D33">
-        <v>40803</v>
+        <v>60608</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I33">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3235,38 +3322,32 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
       <c r="M33" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="P33">
-        <v>96</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="T33">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y33">
         <v>0</v>
@@ -3274,55 +3355,49 @@
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5266</v>
+        <v>2341</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="C34">
-        <v>7108</v>
+        <v>1317</v>
       </c>
       <c r="D34">
-        <v>70901</v>
+        <v>11307</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34">
         <v>12</v>
       </c>
-      <c r="G34" t="s">
-        <v>63</v>
-      </c>
-      <c r="H34" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34">
-        <v>74</v>
-      </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
       <c r="M34" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="N34">
         <v>1</v>
       </c>
       <c r="O34">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="P34">
-        <v>96</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -3337,39 +3412,36 @@
         <v>0</v>
       </c>
       <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>10739</v>
+        <v>14101</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C35">
-        <v>2204</v>
+        <v>5111</v>
       </c>
       <c r="D35">
-        <v>20214</v>
+        <v>51108</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H35" t="s">
         <v>27</v>
       </c>
       <c r="I35">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3381,66 +3453,63 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="N35">
         <v>1</v>
       </c>
       <c r="O35">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="P35">
-        <v>96</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>11029</v>
+        <v>11487</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C36">
-        <v>2103</v>
+        <v>2205</v>
       </c>
       <c r="D36">
-        <v>20206</v>
+        <v>20302</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H36" t="s">
         <v>27</v>
       </c>
       <c r="I36">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -3449,25 +3518,28 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="N36">
         <v>1</v>
       </c>
       <c r="O36">
-        <v>38</v>
-      </c>
-      <c r="P36">
-        <v>2</v>
+        <v>107</v>
+      </c>
+      <c r="P36" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>31</v>
       </c>
       <c r="T36">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -3484,31 +3556,31 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>7595</v>
+        <v>5524</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="C37">
-        <v>5205</v>
+        <v>3209</v>
       </c>
       <c r="D37">
-        <v>50901</v>
+        <v>30803</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H37" t="s">
         <v>27</v>
       </c>
       <c r="I37">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3517,58 +3589,70 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2082</v>
       </c>
       <c r="M37" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37">
-        <v>95</v>
-      </c>
-      <c r="P37">
-        <v>96</v>
+        <v>84</v>
+      </c>
+      <c r="P37" t="s">
+        <v>119</v>
       </c>
       <c r="Q37" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="T37">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2450</v>
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10909</v>
+        <v>3903</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="C38">
-        <v>4205</v>
+        <v>2208</v>
       </c>
       <c r="D38">
-        <v>40704</v>
+        <v>20614</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38">
         <v>27</v>
       </c>
-      <c r="I38">
-        <v>43</v>
-      </c>
       <c r="J38">
         <v>1</v>
       </c>
@@ -3579,31 +3663,37 @@
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="N38">
         <v>2</v>
       </c>
       <c r="O38">
-        <v>70</v>
-      </c>
-      <c r="P38">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="P38" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>31</v>
+      </c>
+      <c r="R38" t="s">
+        <v>81</v>
       </c>
       <c r="T38">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Y38">
         <v>0</v>
@@ -3611,31 +3701,31 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>5146</v>
+        <v>4584</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39">
-        <v>4201</v>
+        <v>6102</v>
       </c>
       <c r="D39">
-        <v>40204</v>
+        <v>60404</v>
       </c>
       <c r="E39">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H39" t="s">
         <v>27</v>
       </c>
       <c r="I39">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -3647,57 +3737,66 @@
         <v>1</v>
       </c>
       <c r="M39" t="s">
+        <v>102</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="O39">
+        <v>65</v>
+      </c>
+      <c r="P39">
+        <v>2</v>
+      </c>
+      <c r="R39" t="s">
         <v>103</v>
       </c>
-      <c r="N39">
-        <v>1</v>
-      </c>
-      <c r="O39">
-        <v>55</v>
-      </c>
-      <c r="P39">
-        <v>2</v>
-      </c>
       <c r="T39">
-        <v>1000000</v>
+        <v>22000</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>3656</v>
+        <v>12157</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>217</v>
       </c>
       <c r="C40">
-        <v>3465</v>
+        <v>2616</v>
       </c>
       <c r="D40">
-        <v>30703</v>
+        <v>20502</v>
       </c>
       <c r="E40">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I40">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -3709,22 +3808,19 @@
         <v>1</v>
       </c>
       <c r="M40" t="s">
-        <v>68</v>
+        <v>218</v>
       </c>
       <c r="N40">
         <v>2</v>
       </c>
       <c r="O40">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="P40">
-        <v>96</v>
-      </c>
-      <c r="R40" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="T40">
-        <v>150000</v>
+        <v>70000</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -3744,31 +3840,28 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>4712</v>
+        <v>14331</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="C41">
-        <v>5103</v>
-      </c>
-      <c r="D41">
-        <v>50609</v>
+        <v>3633</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H41" t="s">
         <v>27</v>
       </c>
       <c r="I41">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3777,66 +3870,69 @@
         <v>1</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M41" t="s">
-        <v>101</v>
+        <v>241</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41">
-        <v>29</v>
-      </c>
-      <c r="P41">
-        <v>7</v>
-      </c>
-      <c r="T41" t="s">
-        <v>34</v>
-      </c>
-      <c r="U41" t="s">
-        <v>34</v>
-      </c>
-      <c r="V41" t="s">
-        <v>34</v>
-      </c>
-      <c r="W41" t="s">
-        <v>34</v>
-      </c>
-      <c r="X41" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>34</v>
+        <v>97</v>
+      </c>
+      <c r="P41" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>31</v>
+      </c>
+      <c r="T41">
+        <v>80000</v>
+      </c>
+      <c r="U41">
+        <v>45000</v>
+      </c>
+      <c r="V41">
+        <v>15000</v>
+      </c>
+      <c r="W41">
+        <v>7000</v>
+      </c>
+      <c r="X41">
+        <v>13000</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>8508</v>
+        <v>10106</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C42">
-        <v>2202</v>
+        <v>4206</v>
       </c>
       <c r="D42">
-        <v>20111</v>
+        <v>40803</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I42">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -3848,34 +3944,34 @@
         <v>1</v>
       </c>
       <c r="M42" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="N42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42">
-        <v>1</v>
-      </c>
-      <c r="P42">
-        <v>96</v>
+        <v>83</v>
+      </c>
+      <c r="P42" t="s">
+        <v>119</v>
       </c>
       <c r="Q42" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -3883,61 +3979,61 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1302</v>
+        <v>12414</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="C43">
-        <v>3111</v>
+        <v>2500</v>
       </c>
       <c r="D43">
-        <v>31101</v>
+        <v>20315</v>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G43" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43">
+        <v>24</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>222</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>49</v>
+      </c>
+      <c r="P43" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q43" t="s">
         <v>31</v>
       </c>
-      <c r="H43" t="s">
-        <v>26</v>
-      </c>
-      <c r="I43">
-        <v>26</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="L43">
-        <v>1</v>
-      </c>
-      <c r="M43" t="s">
-        <v>36</v>
-      </c>
-      <c r="N43">
-        <v>2</v>
-      </c>
-      <c r="O43">
-        <v>82</v>
-      </c>
-      <c r="P43">
-        <v>96</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>37</v>
-      </c>
       <c r="T43">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="U43">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -3954,31 +4050,31 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>11161</v>
+        <v>5266</v>
       </c>
       <c r="B44" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="C44">
-        <v>2208</v>
+        <v>7108</v>
       </c>
       <c r="D44">
-        <v>20614</v>
+        <v>70901</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H44" t="s">
         <v>27</v>
       </c>
       <c r="I44">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -3990,19 +4086,19 @@
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44">
-        <v>24</v>
-      </c>
-      <c r="P44">
-        <v>7</v>
-      </c>
-      <c r="R44" t="s">
-        <v>184</v>
+        <v>65</v>
+      </c>
+      <c r="P44" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>31</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -4025,58 +4121,64 @@
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>2442</v>
+        <v>10739</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="C45">
-        <v>2310</v>
+        <v>2204</v>
       </c>
       <c r="D45">
-        <v>20612</v>
+        <v>20214</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G45" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45">
+        <v>28</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>178</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <v>103</v>
+      </c>
+      <c r="P45" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q45" t="s">
         <v>31</v>
       </c>
-      <c r="H45" t="s">
-        <v>26</v>
-      </c>
-      <c r="I45">
-        <v>25</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-      <c r="K45">
-        <v>1</v>
-      </c>
-      <c r="L45">
-        <v>6</v>
-      </c>
-      <c r="M45" t="s">
-        <v>41</v>
-      </c>
-      <c r="N45">
-        <v>1</v>
-      </c>
-      <c r="O45">
-        <v>110</v>
-      </c>
-      <c r="P45">
-        <v>96</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>42</v>
-      </c>
       <c r="T45">
-        <v>15000</v>
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -4090,25 +4192,25 @@
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>8464</v>
+        <v>11029</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="C46">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="D46">
-        <v>20111</v>
+        <v>20206</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H46" t="s">
         <v>27</v>
@@ -4126,25 +4228,22 @@
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="P46">
         <v>2</v>
       </c>
-      <c r="R46" t="s">
-        <v>150</v>
-      </c>
       <c r="T46">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="U46">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -4161,31 +4260,31 @@
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>7225</v>
+        <v>7595</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C47">
-        <v>2101</v>
+        <v>5205</v>
       </c>
       <c r="D47">
-        <v>20110</v>
+        <v>50901</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F47">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H47" t="s">
         <v>27</v>
       </c>
       <c r="I47">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -4194,66 +4293,60 @@
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="N47">
         <v>2</v>
       </c>
       <c r="O47">
-        <v>53</v>
-      </c>
-      <c r="P47">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="P47" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>31</v>
       </c>
       <c r="T47">
-        <v>1400000</v>
-      </c>
-      <c r="U47" t="s">
-        <v>34</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>0</v>
+        <v>55000</v>
+      </c>
+      <c r="U47">
+        <v>2450</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2900</v>
+        <v>10909</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="C48">
-        <v>1108</v>
+        <v>4205</v>
       </c>
       <c r="D48">
-        <v>11211</v>
+        <v>40704</v>
       </c>
       <c r="E48">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48">
         <v>7</v>
       </c>
       <c r="G48" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="H48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I48">
-        <v>22</v>
+        <v>43</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -4262,19 +4355,19 @@
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>56</v>
+        <v>184</v>
+      </c>
+      <c r="N48">
+        <v>2</v>
       </c>
       <c r="O48">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="P48">
         <v>2</v>
       </c>
-      <c r="R48" t="s">
-        <v>57</v>
-      </c>
       <c r="T48">
-        <v>70000</v>
+        <v>250000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -4294,31 +4387,31 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>770</v>
+        <v>5146</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="C49">
-        <v>5104</v>
+        <v>4201</v>
       </c>
       <c r="D49">
-        <v>50703</v>
+        <v>40204</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="H49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I49">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -4330,66 +4423,57 @@
         <v>1</v>
       </c>
       <c r="M49" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="N49">
         <v>1</v>
       </c>
       <c r="O49">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="P49">
-        <v>96</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="T49">
-        <v>300000</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>5892</v>
+        <v>3656</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="C50">
-        <v>2209</v>
+        <v>3465</v>
       </c>
       <c r="D50">
-        <v>20703</v>
+        <v>30703</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I50">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -4401,48 +4485,66 @@
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="P50">
-        <v>4</v>
+        <v>96</v>
+      </c>
+      <c r="R50" t="s">
+        <v>71</v>
       </c>
       <c r="T50">
-        <v>35000</v>
+        <v>150000</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10305</v>
+        <v>4712</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="C51">
-        <v>4206</v>
+        <v>5103</v>
       </c>
       <c r="D51">
-        <v>40803</v>
+        <v>50609</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I51">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -4454,48 +4556,63 @@
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>166</v>
+        <v>105</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
       </c>
       <c r="O51">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P51">
-        <v>5</v>
-      </c>
-      <c r="R51">
-        <v>3</v>
-      </c>
-      <c r="T51">
-        <v>400000</v>
+        <v>7</v>
+      </c>
+      <c r="T51" t="s">
+        <v>35</v>
+      </c>
+      <c r="U51" t="s">
+        <v>35</v>
+      </c>
+      <c r="V51" t="s">
+        <v>35</v>
+      </c>
+      <c r="W51" t="s">
+        <v>35</v>
+      </c>
+      <c r="X51" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>6538</v>
+        <v>8508</v>
       </c>
       <c r="B52" t="s">
+        <v>156</v>
+      </c>
+      <c r="C52">
+        <v>2202</v>
+      </c>
+      <c r="D52">
+        <v>20111</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>16</v>
+      </c>
+      <c r="G52" t="s">
         <v>122</v>
-      </c>
-      <c r="C52">
-        <v>1201</v>
-      </c>
-      <c r="D52">
-        <v>10207</v>
-      </c>
-      <c r="E52">
-        <v>7</v>
-      </c>
-      <c r="F52">
-        <v>39</v>
-      </c>
-      <c r="G52" t="s">
-        <v>63</v>
       </c>
       <c r="H52" t="s">
         <v>27</v>
       </c>
       <c r="I52">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4503,17 +4620,23 @@
       <c r="K52">
         <v>1</v>
       </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
       <c r="M52" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="N52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52">
-        <v>85</v>
-      </c>
-      <c r="P52">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="P52" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>31</v>
       </c>
       <c r="T52">
         <v>0</v>
@@ -4536,31 +4659,31 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>7585</v>
+        <v>1302</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="C53">
-        <v>5205</v>
+        <v>3111</v>
       </c>
       <c r="D53">
-        <v>50901</v>
+        <v>31101</v>
       </c>
       <c r="E53">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F53">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G53" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I53">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -4572,66 +4695,66 @@
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>92</v>
-      </c>
-      <c r="P53">
-        <v>96</v>
+        <v>82</v>
+      </c>
+      <c r="P53" t="s">
+        <v>38</v>
       </c>
       <c r="Q53" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="T53">
-        <v>150000</v>
-      </c>
-      <c r="U53" t="s">
-        <v>34</v>
-      </c>
-      <c r="V53" t="s">
-        <v>34</v>
-      </c>
-      <c r="W53" t="s">
-        <v>34</v>
-      </c>
-      <c r="X53" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>40000</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>3111</v>
+        <v>11588</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="C54">
-        <v>6201</v>
+        <v>3616</v>
       </c>
       <c r="D54">
-        <v>60303</v>
+        <v>30703</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="G54" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="H54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I54">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -4643,66 +4766,60 @@
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="N54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O54">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="P54">
         <v>2</v>
       </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
       <c r="T54">
-        <v>30000</v>
+        <v>200000</v>
       </c>
       <c r="U54">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10738</v>
+        <v>11382</v>
       </c>
       <c r="B55" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C55">
-        <v>2103</v>
-      </c>
-      <c r="D55">
-        <v>20206</v>
+        <v>3608</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H55" t="s">
         <v>27</v>
       </c>
       <c r="I55">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -4714,66 +4831,63 @@
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="P55">
-        <v>96</v>
-      </c>
-      <c r="R55">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="T55">
+        <v>200000</v>
+      </c>
+      <c r="U55">
         <v>50000</v>
       </c>
-      <c r="U55">
-        <v>0</v>
-      </c>
       <c r="V55">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>4226</v>
+        <v>11161</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="C56">
-        <v>3210</v>
+        <v>2208</v>
       </c>
       <c r="D56">
-        <v>30909</v>
+        <v>20614</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I56">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -4785,63 +4899,66 @@
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="N56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P56">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="R56" t="s">
+        <v>189</v>
       </c>
       <c r="T56">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X56">
         <v>0</v>
       </c>
       <c r="Y56">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>2870</v>
+        <v>11336</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="C57">
-        <v>3206</v>
+        <v>3215</v>
       </c>
       <c r="D57">
-        <v>30604</v>
+        <v>31304</v>
       </c>
       <c r="E57">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G57" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="H57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I57">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -4853,31 +4970,31 @@
         <v>1</v>
       </c>
       <c r="M57" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57">
-        <v>90</v>
-      </c>
-      <c r="P57">
-        <v>96</v>
+        <v>83</v>
+      </c>
+      <c r="P57" t="s">
+        <v>192</v>
       </c>
       <c r="Q57" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="T57">
-        <v>350000</v>
+        <v>13000</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="X57">
         <v>0</v>
@@ -4888,31 +5005,31 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>4243</v>
+        <v>2442</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C58">
-        <v>3210</v>
+        <v>2310</v>
       </c>
       <c r="D58">
-        <v>30909</v>
+        <v>20612</v>
       </c>
       <c r="E58">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G58" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="H58" t="s">
         <v>26</v>
       </c>
       <c r="I58">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -4921,28 +5038,25 @@
         <v>1</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M58" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="N58">
         <v>1</v>
       </c>
       <c r="O58">
+        <v>110</v>
+      </c>
+      <c r="P58" t="s">
         <v>43</v>
       </c>
-      <c r="P58">
-        <v>8</v>
+      <c r="Q58" t="s">
+        <v>31</v>
       </c>
       <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W58">
         <v>0</v>
@@ -4956,31 +5070,31 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>8047</v>
+        <v>8464</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C59">
-        <v>3104</v>
+        <v>2102</v>
       </c>
       <c r="D59">
-        <v>30512</v>
+        <v>20111</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F59">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H59" t="s">
         <v>27</v>
       </c>
       <c r="I59">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -4989,66 +5103,69 @@
         <v>1</v>
       </c>
       <c r="L59">
-        <v>2081</v>
+        <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O59">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="P59">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R59" t="s">
+        <v>155</v>
       </c>
       <c r="T59">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U59">
-        <v>20000</v>
+        <v>1200000</v>
       </c>
       <c r="V59">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>5517</v>
+        <v>7225</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C60">
-        <v>3387</v>
+        <v>2101</v>
       </c>
       <c r="D60">
-        <v>30608</v>
+        <v>20110</v>
       </c>
       <c r="E60">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H60" t="s">
         <v>27</v>
       </c>
       <c r="I60">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -5060,25 +5177,22 @@
         <v>1</v>
       </c>
       <c r="M60" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="P60">
-        <v>96</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
+        <v>1400000</v>
+      </c>
+      <c r="U60" t="s">
+        <v>35</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -5095,31 +5209,31 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>8293</v>
+        <v>13735</v>
       </c>
       <c r="B61" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="C61">
-        <v>7105</v>
+        <v>3549</v>
       </c>
       <c r="D61">
-        <v>70601</v>
+        <v>30802</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F61">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="H61" t="s">
         <v>27</v>
       </c>
       <c r="I61">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -5128,25 +5242,22 @@
         <v>1</v>
       </c>
       <c r="L61">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M61" t="s">
-        <v>146</v>
+        <v>231</v>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O61">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="P61">
-        <v>8</v>
-      </c>
-      <c r="R61" t="s">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="U61">
         <v>0</v>
@@ -5166,67 +5277,61 @@
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>3918</v>
+        <v>2900</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C62">
-        <v>7310</v>
+        <v>1108</v>
       </c>
       <c r="D62">
-        <v>70813</v>
+        <v>11211</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F62">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H62" t="s">
         <v>26</v>
       </c>
       <c r="I62">
-        <v>72</v>
-      </c>
-      <c r="J62">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>80</v>
-      </c>
-      <c r="N62">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="O62">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="P62">
-        <v>4</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>81</v>
+        <v>2</v>
+      </c>
+      <c r="R62" t="s">
+        <v>58</v>
       </c>
       <c r="T62">
-        <v>30000</v>
+        <v>70000</v>
       </c>
       <c r="U62">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -5237,28 +5342,31 @@
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>11382</v>
+        <v>770</v>
       </c>
       <c r="B63" t="s">
-        <v>185</v>
+        <v>28</v>
       </c>
       <c r="C63">
-        <v>3608</v>
+        <v>5104</v>
+      </c>
+      <c r="D63">
+        <v>50703</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G63" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="H63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I63">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -5270,63 +5378,66 @@
         <v>1</v>
       </c>
       <c r="M63" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="N63">
         <v>1</v>
       </c>
       <c r="O63">
-        <v>53</v>
-      </c>
-      <c r="P63">
-        <v>2</v>
+        <v>72</v>
+      </c>
+      <c r="P63" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>31</v>
       </c>
       <c r="T63">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="U63">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>11336</v>
+        <v>5892</v>
       </c>
       <c r="B64" t="s">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="C64">
-        <v>3215</v>
+        <v>2209</v>
       </c>
       <c r="D64">
-        <v>31304</v>
+        <v>20703</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H64" t="s">
         <v>27</v>
       </c>
       <c r="I64">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -5338,60 +5449,45 @@
         <v>1</v>
       </c>
       <c r="M64" t="s">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="N64">
         <v>1</v>
       </c>
       <c r="O64">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="P64">
-        <v>96</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="T64">
-        <v>13000</v>
-      </c>
-      <c r="U64">
-        <v>600</v>
-      </c>
-      <c r="V64">
-        <v>10000</v>
-      </c>
-      <c r="W64">
-        <v>1600</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>11374</v>
+        <v>10305</v>
       </c>
       <c r="B65" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="C65">
-        <v>3501</v>
+        <v>4206</v>
+      </c>
+      <c r="D65">
+        <v>40803</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G65" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I65">
         <v>91</v>
@@ -5406,63 +5502,45 @@
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>191</v>
-      </c>
-      <c r="N65">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="O65">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="P65">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="R65">
+        <v>3</v>
       </c>
       <c r="T65">
-        <v>150000</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>11712</v>
+        <v>13979</v>
       </c>
       <c r="B66" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="C66">
-        <v>3518</v>
-      </c>
-      <c r="D66">
-        <v>30610</v>
+        <v>5611</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F66">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G66" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H66" t="s">
         <v>27</v>
       </c>
       <c r="I66">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -5474,31 +5552,31 @@
         <v>1</v>
       </c>
       <c r="M66" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="N66">
         <v>1</v>
       </c>
       <c r="O66">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="P66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T66">
-        <v>122000</v>
+        <v>0</v>
       </c>
       <c r="U66">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="V66">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="W66">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X66">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="Y66">
         <v>0</v>
@@ -5506,28 +5584,31 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>11880</v>
+        <v>12388</v>
       </c>
       <c r="B67" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C67">
-        <v>3531</v>
+        <v>3604</v>
+      </c>
+      <c r="D67">
+        <v>30608</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H67" t="s">
         <v>27</v>
       </c>
       <c r="I67">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -5539,22 +5620,25 @@
         <v>1</v>
       </c>
       <c r="M67" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2</v>
-      </c>
-      <c r="R67" t="s">
-        <v>196</v>
+        <v>5</v>
       </c>
       <c r="T67">
-        <v>527000</v>
+        <v>60000</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -5568,31 +5652,31 @@
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>11588</v>
+        <v>6538</v>
       </c>
       <c r="B68" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="C68">
-        <v>3616</v>
+        <v>1201</v>
       </c>
       <c r="D68">
-        <v>30703</v>
+        <v>10207</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F68">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G68" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H68" t="s">
         <v>27</v>
       </c>
       <c r="I68">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -5600,23 +5684,20 @@
       <c r="K68">
         <v>1</v>
       </c>
-      <c r="L68">
-        <v>1</v>
-      </c>
       <c r="M68" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="P68">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T68">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -5636,13 +5717,13 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>11903</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>199</v>
+        <v>11973</v>
+      </c>
+      <c r="B69" t="s">
+        <v>212</v>
       </c>
       <c r="C69">
-        <v>4207</v>
+        <v>4107</v>
       </c>
       <c r="D69">
         <v>40806</v>
@@ -5651,16 +5732,16 @@
         <v>14</v>
       </c>
       <c r="F69">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G69" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H69" t="s">
         <v>27</v>
       </c>
       <c r="I69">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -5672,34 +5753,31 @@
         <v>1</v>
       </c>
       <c r="M69" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="N69">
         <v>1</v>
       </c>
       <c r="O69">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>96</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>201</v>
+        <v>4</v>
       </c>
       <c r="T69">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="U69">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="X69">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y69">
         <v>0</v>
@@ -5707,31 +5785,28 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>12157</v>
+        <v>11374</v>
       </c>
       <c r="B70" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C70">
-        <v>2616</v>
-      </c>
-      <c r="D70">
-        <v>20502</v>
+        <v>3501</v>
       </c>
       <c r="E70">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H70" t="s">
         <v>27</v>
       </c>
       <c r="I70">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -5743,19 +5818,19 @@
         <v>1</v>
       </c>
       <c r="M70" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="N70">
         <v>2</v>
       </c>
       <c r="O70">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="P70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T70">
-        <v>70000</v>
+        <v>150000</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -5775,31 +5850,31 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>13733</v>
+        <v>7585</v>
       </c>
       <c r="B71" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="C71">
-        <v>3549</v>
+        <v>5205</v>
       </c>
       <c r="D71">
-        <v>30802</v>
+        <v>50901</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F71">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H71" t="s">
         <v>27</v>
       </c>
       <c r="I71">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -5811,63 +5886,66 @@
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="N71">
         <v>1</v>
       </c>
       <c r="O71">
-        <v>78</v>
-      </c>
-      <c r="P71">
-        <v>2</v>
+        <v>92</v>
+      </c>
+      <c r="P71" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>31</v>
       </c>
       <c r="T71">
-        <v>50000</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
+        <v>150000</v>
+      </c>
+      <c r="U71" t="s">
+        <v>35</v>
+      </c>
+      <c r="V71" t="s">
+        <v>35</v>
+      </c>
+      <c r="W71" t="s">
+        <v>35</v>
+      </c>
+      <c r="X71" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>13735</v>
+        <v>3111</v>
       </c>
       <c r="B72" t="s">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="C72">
-        <v>3549</v>
+        <v>6201</v>
       </c>
       <c r="D72">
-        <v>30802</v>
+        <v>60303</v>
       </c>
       <c r="E72">
+        <v>5</v>
+      </c>
+      <c r="F72">
         <v>14</v>
       </c>
-      <c r="F72">
-        <v>31</v>
-      </c>
       <c r="G72" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="H72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I72">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -5879,114 +5957,865 @@
         <v>1</v>
       </c>
       <c r="M72" t="s">
-        <v>207</v>
+        <v>63</v>
       </c>
       <c r="N72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P72">
         <v>2</v>
       </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
       <c r="T72">
-        <v>35000</v>
+        <v>30000</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>13570</v>
+        <v>10738</v>
       </c>
       <c r="B73" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="C73">
-        <v>2600</v>
+        <v>2103</v>
       </c>
       <c r="D73">
-        <v>20315</v>
+        <v>20206</v>
       </c>
       <c r="E73">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F73">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="G73" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H73" t="s">
         <v>27</v>
       </c>
       <c r="I73">
+        <v>28</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
+        <v>176</v>
+      </c>
+      <c r="N73">
+        <v>2</v>
+      </c>
+      <c r="O73">
+        <v>65</v>
+      </c>
+      <c r="P73">
+        <v>96</v>
+      </c>
+      <c r="R73">
+        <v>96</v>
+      </c>
+      <c r="T73">
+        <v>50000</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>4226</v>
+      </c>
+      <c r="B74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74">
+        <v>3210</v>
+      </c>
+      <c r="D74">
+        <v>30909</v>
+      </c>
+      <c r="E74">
+        <v>10</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74" t="s">
+        <v>64</v>
+      </c>
+      <c r="H74" t="s">
+        <v>26</v>
+      </c>
+      <c r="I74">
+        <v>51</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>94</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74">
+        <v>20</v>
+      </c>
+      <c r="P74">
+        <v>3</v>
+      </c>
+      <c r="T74">
+        <v>55000</v>
+      </c>
+      <c r="U74">
+        <v>15000</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>5000</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2870</v>
+      </c>
+      <c r="B75" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75">
+        <v>3206</v>
+      </c>
+      <c r="D75">
+        <v>30604</v>
+      </c>
+      <c r="E75">
+        <v>11</v>
+      </c>
+      <c r="F75">
+        <v>11</v>
+      </c>
+      <c r="G75" t="s">
+        <v>50</v>
+      </c>
+      <c r="H75" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75">
+        <v>91</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75" t="s">
+        <v>54</v>
+      </c>
+      <c r="N75">
+        <v>2</v>
+      </c>
+      <c r="O75">
+        <v>90</v>
+      </c>
+      <c r="P75" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>31</v>
+      </c>
+      <c r="T75">
+        <v>350000</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>4243</v>
+      </c>
+      <c r="B76" t="s">
+        <v>95</v>
+      </c>
+      <c r="C76">
+        <v>3210</v>
+      </c>
+      <c r="D76">
+        <v>30909</v>
+      </c>
+      <c r="E76">
+        <v>10</v>
+      </c>
+      <c r="F76">
+        <v>4</v>
+      </c>
+      <c r="G76" t="s">
+        <v>64</v>
+      </c>
+      <c r="H76" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76">
+        <v>53</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76" t="s">
+        <v>96</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76">
+        <v>43</v>
+      </c>
+      <c r="P76">
+        <v>8</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>8047</v>
+      </c>
+      <c r="B77" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77">
+        <v>3104</v>
+      </c>
+      <c r="D77">
+        <v>30512</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>13</v>
+      </c>
+      <c r="G77" t="s">
+        <v>64</v>
+      </c>
+      <c r="H77" t="s">
+        <v>27</v>
+      </c>
+      <c r="I77">
+        <v>57</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>2081</v>
+      </c>
+      <c r="M77" t="s">
+        <v>149</v>
+      </c>
+      <c r="N77">
+        <v>1</v>
+      </c>
+      <c r="O77">
+        <v>75</v>
+      </c>
+      <c r="P77">
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <v>50000</v>
+      </c>
+      <c r="U77">
+        <v>20000</v>
+      </c>
+      <c r="V77">
+        <v>80000</v>
+      </c>
+      <c r="W77">
+        <v>2000</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>13570</v>
+      </c>
+      <c r="B78" t="s">
+        <v>224</v>
+      </c>
+      <c r="C78">
+        <v>2600</v>
+      </c>
+      <c r="D78">
+        <v>20315</v>
+      </c>
+      <c r="E78">
+        <v>8</v>
+      </c>
+      <c r="F78">
+        <v>44</v>
+      </c>
+      <c r="G78" t="s">
+        <v>122</v>
+      </c>
+      <c r="H78" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78">
         <v>24</v>
       </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="K73">
-        <v>1</v>
-      </c>
-      <c r="L73">
-        <v>1</v>
-      </c>
-      <c r="M73" t="s">
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78" t="s">
+        <v>225</v>
+      </c>
+      <c r="N78">
+        <v>2</v>
+      </c>
+      <c r="O78">
+        <v>77</v>
+      </c>
+      <c r="P78" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>31</v>
+      </c>
+      <c r="R78" t="s">
+        <v>227</v>
+      </c>
+      <c r="T78">
+        <v>150000</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>5517</v>
+      </c>
+      <c r="B79" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79">
+        <v>3387</v>
+      </c>
+      <c r="D79">
+        <v>30608</v>
+      </c>
+      <c r="E79">
+        <v>30</v>
+      </c>
+      <c r="F79">
+        <v>20</v>
+      </c>
+      <c r="G79" t="s">
+        <v>64</v>
+      </c>
+      <c r="H79" t="s">
+        <v>27</v>
+      </c>
+      <c r="I79">
+        <v>94</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>115</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79">
+        <v>72</v>
+      </c>
+      <c r="P79">
+        <v>96</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>116</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>11903</v>
+      </c>
+      <c r="B80" t="s">
+        <v>207</v>
+      </c>
+      <c r="C80">
+        <v>4207</v>
+      </c>
+      <c r="D80">
+        <v>40806</v>
+      </c>
+      <c r="E80">
+        <v>14</v>
+      </c>
+      <c r="F80">
+        <v>36</v>
+      </c>
+      <c r="G80" t="s">
+        <v>122</v>
+      </c>
+      <c r="H80" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80">
+        <v>26</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80" t="s">
+        <v>208</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80">
+        <v>64</v>
+      </c>
+      <c r="P80" t="s">
         <v>209</v>
       </c>
-      <c r="N73">
-        <v>2</v>
-      </c>
-      <c r="O73">
-        <v>77</v>
-      </c>
-      <c r="P73" t="s">
+      <c r="Q80" t="s">
+        <v>31</v>
+      </c>
+      <c r="T80">
+        <v>50000</v>
+      </c>
+      <c r="U80">
+        <v>30000</v>
+      </c>
+      <c r="V80">
+        <v>20000</v>
+      </c>
+      <c r="W80">
+        <v>3000</v>
+      </c>
+      <c r="X80">
+        <v>10000</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>11931</v>
+      </c>
+      <c r="B81" t="s">
         <v>210</v>
       </c>
-      <c r="Q73">
-        <v>96</v>
-      </c>
-      <c r="R73" t="s">
+      <c r="C81">
+        <v>7203</v>
+      </c>
+      <c r="D81">
+        <v>70403</v>
+      </c>
+      <c r="E81">
+        <v>7</v>
+      </c>
+      <c r="F81">
+        <v>28</v>
+      </c>
+      <c r="G81" t="s">
+        <v>122</v>
+      </c>
+      <c r="H81" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81">
+        <v>72</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81" t="s">
         <v>211</v>
       </c>
-      <c r="T73">
-        <v>150000</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73">
-        <v>0</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81">
+        <v>65</v>
+      </c>
+      <c r="P81">
+        <v>2</v>
+      </c>
+      <c r="T81">
+        <v>10000</v>
+      </c>
+      <c r="U81">
+        <v>25000</v>
+      </c>
+      <c r="V81">
+        <v>10000</v>
+      </c>
+      <c r="W81">
+        <v>8000</v>
+      </c>
+      <c r="X81">
+        <v>10000</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>14148</v>
+      </c>
+      <c r="B82" t="s">
+        <v>236</v>
+      </c>
+      <c r="C82">
+        <v>3550</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>50</v>
+      </c>
+      <c r="G82" t="s">
+        <v>122</v>
+      </c>
+      <c r="H82" t="s">
+        <v>27</v>
+      </c>
+      <c r="I82">
+        <v>56</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>4</v>
+      </c>
+      <c r="M82" t="s">
+        <v>237</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82">
+        <v>79</v>
+      </c>
+      <c r="P82">
+        <v>2</v>
+      </c>
+      <c r="T82">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>8293</v>
+      </c>
+      <c r="B83" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83">
+        <v>7105</v>
+      </c>
+      <c r="D83">
+        <v>70601</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>11</v>
+      </c>
+      <c r="G83" t="s">
+        <v>64</v>
+      </c>
+      <c r="H83" t="s">
+        <v>27</v>
+      </c>
+      <c r="I83">
+        <v>72</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="L83">
+        <v>8</v>
+      </c>
+      <c r="M83" t="s">
+        <v>151</v>
+      </c>
+      <c r="N83">
+        <v>2</v>
+      </c>
+      <c r="O83">
+        <v>72</v>
+      </c>
+      <c r="P83">
+        <v>8</v>
+      </c>
+      <c r="R83" t="s">
+        <v>152</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>3918</v>
+      </c>
+      <c r="B84" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84">
+        <v>7310</v>
+      </c>
+      <c r="D84">
+        <v>70813</v>
+      </c>
+      <c r="E84">
+        <v>4</v>
+      </c>
+      <c r="F84">
+        <v>9</v>
+      </c>
+      <c r="G84" t="s">
+        <v>64</v>
+      </c>
+      <c r="H84" t="s">
+        <v>26</v>
+      </c>
+      <c r="I84">
+        <v>72</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84" t="s">
+        <v>83</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84">
+        <v>95</v>
+      </c>
+      <c r="P84" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>85</v>
+      </c>
+      <c r="T84">
+        <v>30000</v>
+      </c>
+      <c r="U84">
+        <v>20000</v>
+      </c>
+      <c r="V84">
+        <v>25000</v>
+      </c>
+      <c r="W84">
+        <v>5000</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y62">
-    <sortCondition ref="M1:M62"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y4146">
+    <sortCondition ref="M1:M4146"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset/PART 2_3_ Mortality (Death) Information.xlsx
+++ b/dataset/PART 2_3_ Mortality (Death) Information.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\2025-12-10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khagendra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5C23F7-1C7D-4EC4-BE04-0C823AD8CC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF647C2-B727-4405-9696-9940E610D5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="247">
   <si>
     <t>ID</t>
   </si>
@@ -228,9 +228,6 @@
     <t>v5</t>
   </si>
   <si>
-    <t>02</t>
-  </si>
-  <si>
     <t>bc7381d5-b43c-49bb-b6bb-ac8d8b051795</t>
   </si>
   <si>
@@ -760,6 +757,21 @@
   </si>
   <si>
     <t>NORMAL</t>
+  </si>
+  <si>
+    <t>9e54c2bb-5780-4f94-bb00-c1e8815079ec</t>
+  </si>
+  <si>
+    <t>HIRA MAYA DANGOL</t>
+  </si>
+  <si>
+    <t>190763ff-3d00-441e-bce6-f56d4958f134</t>
+  </si>
+  <si>
+    <t>DAN BAHADUR MAHARJAN</t>
+  </si>
+  <si>
+    <t>HART PROBLEM</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y84"/>
+  <dimension ref="A1:Y86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1218,7 +1230,7 @@
         <v>6671</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C2">
         <v>4108</v>
@@ -1251,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -1260,13 +1272,13 @@
         <v>98</v>
       </c>
       <c r="P2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q2" t="s">
         <v>31</v>
       </c>
       <c r="R2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T2">
         <v>18000</v>
@@ -1292,7 +1304,7 @@
         <v>5150</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3">
         <v>6204</v>
@@ -1325,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -1334,7 +1346,7 @@
         <v>82</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q3" t="s">
         <v>31</v>
@@ -1363,7 +1375,7 @@
         <v>3683</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>1415</v>
@@ -1396,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N4">
         <v>2</v>
@@ -1431,7 +1443,7 @@
         <v>10769</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C5">
         <v>2103</v>
@@ -1446,7 +1458,7 @@
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H5" t="s">
         <v>27</v>
@@ -1464,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -1476,7 +1488,7 @@
         <v>2</v>
       </c>
       <c r="R5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="T5">
         <v>50000</v>
@@ -1502,7 +1514,7 @@
         <v>11712</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C6">
         <v>3518</v>
@@ -1517,7 +1529,7 @@
         <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H6" t="s">
         <v>27</v>
@@ -1535,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1570,7 +1582,7 @@
         <v>13733</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C7">
         <v>3549</v>
@@ -1578,14 +1590,14 @@
       <c r="D7">
         <v>30802</v>
       </c>
-      <c r="E7" t="s">
-        <v>65</v>
+      <c r="E7">
+        <v>2</v>
       </c>
       <c r="F7">
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H7" t="s">
         <v>27</v>
@@ -1603,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -1638,7 +1650,7 @@
         <v>4581</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8">
         <v>6202</v>
@@ -1671,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -1706,7 +1718,7 @@
         <v>3356</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>5102</v>
@@ -1739,13 +1751,13 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="R9" t="s">
         <v>67</v>
-      </c>
-      <c r="N9">
-        <v>2</v>
-      </c>
-      <c r="R9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -1753,7 +1765,7 @@
         <v>6013</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10">
         <v>6204</v>
@@ -1786,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N10">
         <v>1</v>
@@ -1886,31 +1898,31 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10611</v>
+        <v>14461</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="C12">
-        <v>2103</v>
+        <v>3649</v>
       </c>
       <c r="D12">
-        <v>20206</v>
+        <v>30802</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
       </c>
       <c r="I12">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1922,66 +1934,51 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>246</v>
       </c>
       <c r="Q12" t="s">
         <v>31</v>
       </c>
       <c r="T12">
-        <v>4000</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>7110</v>
+        <v>10611</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C13">
-        <v>7109</v>
+        <v>2103</v>
       </c>
       <c r="D13">
-        <v>70909</v>
+        <v>20206</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I13">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1993,66 +1990,66 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="P13" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="Q13" t="s">
         <v>31</v>
       </c>
       <c r="T13">
-        <v>200000</v>
+        <v>4000</v>
       </c>
       <c r="U13">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>992</v>
+        <v>7110</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="C14">
-        <v>3201</v>
+        <v>7109</v>
       </c>
       <c r="D14">
-        <v>30102</v>
+        <v>70909</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H14" t="s">
         <v>26</v>
       </c>
       <c r="I14">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2064,54 +2061,57 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="O14">
-        <v>32</v>
-      </c>
-      <c r="P14">
-        <v>4</v>
+        <v>46</v>
+      </c>
+      <c r="P14" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>31</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
-        <v>35</v>
+        <v>20000</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2585</v>
+        <v>992</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C15">
-        <v>7206</v>
+        <v>3201</v>
       </c>
       <c r="D15">
-        <v>70811</v>
+        <v>30102</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
         <v>32</v>
@@ -2120,7 +2120,7 @@
         <v>26</v>
       </c>
       <c r="I15">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2132,16 +2132,16 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -2149,8 +2149,8 @@
       <c r="U15">
         <v>0</v>
       </c>
-      <c r="V15">
-        <v>0</v>
+      <c r="V15" t="s">
+        <v>35</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -2164,13 +2164,13 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2591</v>
+        <v>2585</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16">
-        <v>7106</v>
+        <v>7206</v>
       </c>
       <c r="D16">
         <v>70811</v>
@@ -2179,7 +2179,7 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
         <v>32</v>
@@ -2206,22 +2206,22 @@
         <v>1</v>
       </c>
       <c r="O16">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X16">
         <v>0</v>
@@ -2232,31 +2232,31 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>6967</v>
+        <v>2591</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="C17">
-        <v>6106</v>
+        <v>7106</v>
       </c>
       <c r="D17">
-        <v>60806</v>
+        <v>70811</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I17">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2268,31 +2268,28 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
       <c r="O17">
-        <v>82</v>
-      </c>
-      <c r="P17" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>31</v>
+        <v>54</v>
+      </c>
+      <c r="P17">
+        <v>4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X17">
         <v>0</v>
@@ -2303,31 +2300,31 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9715</v>
+        <v>6967</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="C18">
-        <v>2104</v>
+        <v>6106</v>
       </c>
       <c r="D18">
-        <v>20214</v>
+        <v>60806</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
         <v>27</v>
       </c>
       <c r="I18">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2339,19 +2336,22 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>70</v>
-      </c>
-      <c r="P18">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="P18" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>31</v>
       </c>
       <c r="T18">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -2371,31 +2371,31 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9158</v>
+        <v>9715</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C19">
-        <v>3204</v>
+        <v>2104</v>
       </c>
       <c r="D19">
-        <v>30512</v>
+        <v>20214</v>
       </c>
       <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
         <v>4</v>
       </c>
-      <c r="F19">
-        <v>7</v>
-      </c>
       <c r="G19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H19" t="s">
         <v>27</v>
       </c>
       <c r="I19">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2404,51 +2404,66 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="T19">
+        <v>70000</v>
       </c>
       <c r="U19">
-        <v>300000</v>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>11990</v>
+        <v>9158</v>
       </c>
       <c r="B20" t="s">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="C20">
-        <v>4107</v>
+        <v>3204</v>
       </c>
       <c r="D20">
-        <v>40806</v>
+        <v>30512</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s">
         <v>27</v>
       </c>
       <c r="I20">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2457,108 +2472,90 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M20" t="s">
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="P20">
-        <v>7</v>
-      </c>
-      <c r="R20" t="s">
-        <v>216</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>3862</v>
+        <v>11990</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="C21">
-        <v>1315</v>
+        <v>4107</v>
       </c>
       <c r="D21">
-        <v>11213</v>
+        <v>40806</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21">
+        <v>51</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>214</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21">
         <v>26</v>
       </c>
-      <c r="I21">
-        <v>24</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21" t="s">
-        <v>75</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>25</v>
-      </c>
-      <c r="P21" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>77</v>
+      <c r="P21">
+        <v>7</v>
+      </c>
+      <c r="R21" t="s">
+        <v>215</v>
       </c>
       <c r="T21">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="Y21">
         <v>0</v>
@@ -2566,61 +2563,70 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>11880</v>
+        <v>3862</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="C22">
-        <v>3531</v>
+        <v>1315</v>
+      </c>
+      <c r="D22">
+        <v>11213</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22">
+        <v>24</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>74</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
         <v>25</v>
       </c>
-      <c r="G22" t="s">
-        <v>122</v>
-      </c>
-      <c r="H22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22">
-        <v>58</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N22">
-        <v>2</v>
-      </c>
-      <c r="O22">
-        <v>62</v>
-      </c>
-      <c r="P22">
-        <v>2</v>
-      </c>
-      <c r="R22" t="s">
-        <v>206</v>
+      <c r="P22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>76</v>
       </c>
       <c r="T22">
-        <v>527000</v>
+        <v>60000</v>
+      </c>
+      <c r="U22">
+        <v>200000</v>
+      </c>
+      <c r="V22">
+        <v>120000</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="Y22">
         <v>0</v>
@@ -2628,31 +2634,31 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>3061</v>
+        <v>11880</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>203</v>
       </c>
       <c r="C23">
-        <v>4103</v>
+        <v>3531</v>
       </c>
       <c r="D23">
-        <v>40602</v>
+        <v>30802</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I23">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2664,31 +2670,28 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R23" t="s">
+        <v>205</v>
       </c>
       <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
+        <v>527000</v>
       </c>
       <c r="W23">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y23">
         <v>0</v>
@@ -2696,31 +2699,31 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4509</v>
+        <v>3061</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="C24">
-        <v>3205</v>
+        <v>4103</v>
       </c>
       <c r="D24">
-        <v>30601</v>
+        <v>40602</v>
       </c>
       <c r="E24">
         <v>4</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="H24" t="s">
         <v>26</v>
       </c>
       <c r="I24">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2732,63 +2735,63 @@
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="N24">
         <v>1</v>
       </c>
       <c r="O24">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="X24">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="Y24">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>7464</v>
+        <v>4509</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="C25">
-        <v>5105</v>
+        <v>3205</v>
       </c>
       <c r="D25">
-        <v>50901</v>
+        <v>30601</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
         <v>64</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I25">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2800,63 +2803,63 @@
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="P25">
         <v>2</v>
       </c>
       <c r="T25">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="U25">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="V25">
-        <v>16000</v>
+        <v>150000</v>
       </c>
       <c r="W25">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="X25">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3977</v>
+        <v>14409</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C26">
-        <v>2208</v>
+        <v>3459</v>
       </c>
       <c r="D26">
-        <v>20614</v>
+        <v>30802</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I26">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2868,42 +2871,36 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>80</v>
-      </c>
-      <c r="P26" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>31</v>
+        <v>82</v>
+      </c>
+      <c r="P26">
+        <v>2</v>
       </c>
       <c r="T26">
-        <v>40000</v>
-      </c>
-      <c r="U26">
-        <v>16000</v>
+        <v>280000</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>8786</v>
+        <v>7464</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C27">
-        <v>1101</v>
+        <v>5105</v>
       </c>
       <c r="D27">
-        <v>10207</v>
+        <v>50901</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>14</v>
@@ -2915,7 +2912,7 @@
         <v>27</v>
       </c>
       <c r="I27">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2927,34 +2924,31 @@
         <v>1</v>
       </c>
       <c r="M27" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27">
-        <v>73</v>
-      </c>
-      <c r="P27" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>31</v>
+        <v>71</v>
+      </c>
+      <c r="P27">
+        <v>2</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="Y27">
         <v>0</v>
@@ -2962,22 +2956,22 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4161</v>
+        <v>3977</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C28">
-        <v>1109</v>
+        <v>2208</v>
       </c>
       <c r="D28">
-        <v>11214</v>
+        <v>20614</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G28" t="s">
         <v>64</v>
@@ -2986,7 +2980,7 @@
         <v>26</v>
       </c>
       <c r="I28">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2998,63 +2992,54 @@
         <v>1</v>
       </c>
       <c r="M28" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N28">
         <v>1</v>
       </c>
       <c r="O28">
-        <v>85</v>
-      </c>
-      <c r="P28">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="P28" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>31</v>
       </c>
       <c r="T28">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="U28">
-        <v>30000</v>
-      </c>
-      <c r="V28">
-        <v>15000</v>
-      </c>
-      <c r="W28">
-        <v>5000</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>4076</v>
+        <v>8786</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="C29">
-        <v>2108</v>
+        <v>1101</v>
       </c>
       <c r="D29">
-        <v>20614</v>
+        <v>10207</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
         <v>64</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I29">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -3066,63 +3051,66 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="N29">
         <v>1</v>
       </c>
       <c r="O29">
-        <v>50</v>
-      </c>
-      <c r="P29">
-        <v>2</v>
+        <v>73</v>
+      </c>
+      <c r="P29" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>31</v>
       </c>
       <c r="T29">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>14305</v>
+        <v>4161</v>
       </c>
       <c r="B30" t="s">
-        <v>238</v>
+        <v>90</v>
       </c>
       <c r="C30">
-        <v>3481</v>
+        <v>1109</v>
       </c>
       <c r="D30">
-        <v>30802</v>
+        <v>11214</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F30">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I30">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3134,28 +3122,28 @@
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="N30">
         <v>1</v>
       </c>
       <c r="O30">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P30">
         <v>2</v>
       </c>
       <c r="T30">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X30">
         <v>0</v>
@@ -3166,31 +3154,31 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2634</v>
+        <v>4076</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C31">
-        <v>1109</v>
+        <v>2108</v>
       </c>
       <c r="D31">
-        <v>11214</v>
+        <v>20614</v>
       </c>
       <c r="E31">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H31" t="s">
         <v>26</v>
       </c>
       <c r="I31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3202,51 +3190,63 @@
         <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="N31">
         <v>1</v>
       </c>
       <c r="O31">
-        <v>80</v>
-      </c>
-      <c r="P31" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
       </c>
       <c r="T31">
-        <v>15000</v>
+        <v>50000</v>
+      </c>
+      <c r="U31">
+        <v>20000</v>
+      </c>
+      <c r="V31">
+        <v>20000</v>
+      </c>
+      <c r="W31">
+        <v>5000</v>
+      </c>
+      <c r="X31">
+        <v>5000</v>
+      </c>
+      <c r="Y31">
+        <v>30000</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>9655</v>
+        <v>14305</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="C32">
-        <v>1206</v>
+        <v>3459</v>
       </c>
       <c r="D32">
-        <v>11005</v>
+        <v>30802</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I32">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3258,31 +3258,31 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>165</v>
+        <v>238</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="P32">
         <v>2</v>
       </c>
       <c r="T32">
-        <v>560000</v>
+        <v>200000</v>
       </c>
       <c r="U32">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y32">
         <v>0</v>
@@ -3290,31 +3290,31 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5998</v>
+        <v>2634</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="C33">
-        <v>6204</v>
+        <v>1109</v>
       </c>
       <c r="D33">
-        <v>60608</v>
+        <v>11214</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I33">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3322,64 +3322,55 @@
       <c r="K33">
         <v>1</v>
       </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="N33">
         <v>1</v>
       </c>
       <c r="O33">
-        <v>68</v>
-      </c>
-      <c r="P33">
-        <v>4</v>
+        <v>80</v>
+      </c>
+      <c r="P33" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>31</v>
       </c>
       <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2341</v>
+        <v>9655</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c r="C34">
-        <v>1317</v>
+        <v>1206</v>
       </c>
       <c r="D34">
-        <v>11307</v>
+        <v>11005</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="H34" t="s">
         <v>26</v>
       </c>
       <c r="I34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3387,61 +3378,67 @@
       <c r="K34">
         <v>1</v>
       </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
       <c r="M34" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="P34">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>560000</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="X34">
+        <v>10000</v>
+      </c>
+      <c r="Y34">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>14101</v>
+        <v>5998</v>
       </c>
       <c r="B35" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="C35">
-        <v>5111</v>
+        <v>6204</v>
       </c>
       <c r="D35">
-        <v>51108</v>
+        <v>60608</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H35" t="s">
         <v>27</v>
       </c>
       <c r="I35">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3449,67 +3446,64 @@
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="L35">
-        <v>1</v>
-      </c>
       <c r="M35" t="s">
-        <v>235</v>
+        <v>123</v>
       </c>
       <c r="N35">
         <v>1</v>
       </c>
       <c r="O35">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T35">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>60000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>11487</v>
+        <v>2341</v>
       </c>
       <c r="B36" t="s">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="C36">
-        <v>2205</v>
+        <v>1317</v>
       </c>
       <c r="D36">
-        <v>20302</v>
+        <v>11307</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
         <v>26</v>
       </c>
-      <c r="G36" t="s">
-        <v>122</v>
-      </c>
-      <c r="H36" t="s">
-        <v>27</v>
-      </c>
       <c r="I36">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -3517,29 +3511,23 @@
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="L36">
+      <c r="M36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>90</v>
+      </c>
+      <c r="P36">
         <v>8</v>
       </c>
-      <c r="M36" t="s">
-        <v>198</v>
-      </c>
-      <c r="N36">
-        <v>1</v>
-      </c>
-      <c r="O36">
-        <v>107</v>
-      </c>
-      <c r="P36" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>31</v>
-      </c>
       <c r="T36">
         <v>0</v>
       </c>
       <c r="U36">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -3548,39 +3536,36 @@
         <v>0</v>
       </c>
       <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>5524</v>
+        <v>14101</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="C37">
-        <v>3209</v>
+        <v>5111</v>
       </c>
       <c r="D37">
-        <v>30803</v>
+        <v>51104</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H37" t="s">
         <v>27</v>
       </c>
       <c r="I37">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3589,69 +3574,66 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>2082</v>
+        <v>1</v>
       </c>
       <c r="M37" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="N37">
         <v>1</v>
       </c>
       <c r="O37">
-        <v>84</v>
-      </c>
-      <c r="P37" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>31</v>
+        <v>71</v>
+      </c>
+      <c r="P37">
+        <v>2</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3903</v>
+        <v>11487</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="C38">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="D38">
-        <v>20614</v>
+        <v>20302</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I38">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -3660,40 +3642,37 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M38" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="P38" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="Q38" t="s">
         <v>31</v>
       </c>
-      <c r="R38" t="s">
-        <v>81</v>
-      </c>
       <c r="T38">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>200000</v>
+        <v>3000</v>
       </c>
       <c r="V38">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="Y38">
         <v>0</v>
@@ -3701,22 +3680,22 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>4584</v>
+        <v>5524</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C39">
-        <v>6102</v>
+        <v>3209</v>
       </c>
       <c r="D39">
-        <v>60404</v>
+        <v>30803</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F39">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G39" t="s">
         <v>64</v>
@@ -3725,7 +3704,7 @@
         <v>27</v>
       </c>
       <c r="I39">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -3734,25 +3713,25 @@
         <v>1</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>2082</v>
       </c>
       <c r="M39" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39">
-        <v>65</v>
-      </c>
-      <c r="P39">
-        <v>2</v>
-      </c>
-      <c r="R39" t="s">
-        <v>103</v>
+        <v>84</v>
+      </c>
+      <c r="P39" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>31</v>
       </c>
       <c r="T39">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -3772,32 +3751,32 @@
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>12157</v>
+        <v>3903</v>
       </c>
       <c r="B40" t="s">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="C40">
-        <v>2616</v>
+        <v>2208</v>
       </c>
       <c r="D40">
-        <v>20502</v>
+        <v>20614</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H40" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40">
         <v>27</v>
       </c>
-      <c r="I40">
-        <v>22</v>
-      </c>
       <c r="J40">
         <v>1</v>
       </c>
@@ -3808,31 +3787,37 @@
         <v>1</v>
       </c>
       <c r="M40" t="s">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="N40">
         <v>2</v>
       </c>
       <c r="O40">
-        <v>82</v>
-      </c>
-      <c r="P40">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="P40" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>31</v>
+      </c>
+      <c r="R40" t="s">
+        <v>80</v>
       </c>
       <c r="T40">
-        <v>70000</v>
+        <v>300000</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Y40">
         <v>0</v>
@@ -3840,28 +3825,31 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>14331</v>
+        <v>4584</v>
       </c>
       <c r="B41" t="s">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="C41">
-        <v>3633</v>
+        <v>6102</v>
+      </c>
+      <c r="D41">
+        <v>60404</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H41" t="s">
         <v>27</v>
       </c>
       <c r="I41">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3870,37 +3858,37 @@
         <v>1</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="N41">
         <v>2</v>
       </c>
       <c r="O41">
-        <v>97</v>
-      </c>
-      <c r="P41" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>31</v>
+        <v>65</v>
+      </c>
+      <c r="P41">
+        <v>2</v>
+      </c>
+      <c r="R41" t="s">
+        <v>102</v>
       </c>
       <c r="T41">
-        <v>80000</v>
+        <v>22000</v>
       </c>
       <c r="U41">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="Y41">
         <v>0</v>
@@ -3908,31 +3896,31 @@
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10106</v>
+        <v>12157</v>
       </c>
       <c r="B42" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="C42">
-        <v>4206</v>
+        <v>2617</v>
       </c>
       <c r="D42">
-        <v>40803</v>
+        <v>20514</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="G42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I42">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -3944,34 +3932,31 @@
         <v>1</v>
       </c>
       <c r="M42" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="N42">
         <v>2</v>
       </c>
       <c r="O42">
-        <v>83</v>
-      </c>
-      <c r="P42" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>31</v>
+        <v>82</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
       </c>
       <c r="T42">
-        <v>10000</v>
+        <v>70000</v>
       </c>
       <c r="U42">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -3979,31 +3964,31 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>12414</v>
+        <v>14331</v>
       </c>
       <c r="B43" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C43">
-        <v>2500</v>
+        <v>3649</v>
       </c>
       <c r="D43">
-        <v>20315</v>
+        <v>30802</v>
       </c>
       <c r="E43">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H43" t="s">
         <v>27</v>
       </c>
       <c r="I43">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -4012,37 +3997,37 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M43" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="P43" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="Q43" t="s">
         <v>31</v>
       </c>
       <c r="T43">
-        <v>53000</v>
+        <v>80000</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -4050,31 +4035,31 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>5266</v>
+        <v>10106</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="C44">
-        <v>7108</v>
+        <v>4206</v>
       </c>
       <c r="D44">
-        <v>70901</v>
+        <v>40803</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I44">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -4086,34 +4071,34 @@
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="P44" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="Q44" t="s">
         <v>31</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Y44">
         <v>0</v>
@@ -4121,31 +4106,31 @@
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10739</v>
+        <v>12414</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="C45">
-        <v>2204</v>
+        <v>2500</v>
       </c>
       <c r="D45">
-        <v>20214</v>
+        <v>20315</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H45" t="s">
         <v>27</v>
       </c>
       <c r="I45">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -4157,22 +4142,22 @@
         <v>1</v>
       </c>
       <c r="M45" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="N45">
         <v>1</v>
       </c>
       <c r="O45">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="Q45" t="s">
         <v>31</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="U45">
         <v>0</v>
@@ -4192,31 +4177,31 @@
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>11029</v>
+        <v>5266</v>
       </c>
       <c r="B46" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="C46">
-        <v>2103</v>
+        <v>7108</v>
       </c>
       <c r="D46">
-        <v>20206</v>
+        <v>70901</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
       <c r="F46">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H46" t="s">
         <v>27</v>
       </c>
       <c r="I46">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -4228,19 +4213,22 @@
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="N46">
         <v>1</v>
       </c>
       <c r="O46">
-        <v>38</v>
-      </c>
-      <c r="P46">
-        <v>2</v>
+        <v>65</v>
+      </c>
+      <c r="P46" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>31</v>
       </c>
       <c r="T46">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -4260,31 +4248,31 @@
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>7595</v>
+        <v>10739</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="C47">
-        <v>5205</v>
+        <v>2204</v>
       </c>
       <c r="D47">
-        <v>50901</v>
+        <v>20214</v>
       </c>
       <c r="E47">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F47">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H47" t="s">
         <v>27</v>
       </c>
       <c r="I47">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -4293,57 +4281,69 @@
         <v>1</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="P47" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="Q47" t="s">
         <v>31</v>
       </c>
       <c r="T47">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2450</v>
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10909</v>
+        <v>11029</v>
       </c>
       <c r="B48" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C48">
-        <v>4205</v>
+        <v>2103</v>
       </c>
       <c r="D48">
-        <v>40704</v>
+        <v>20206</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H48" t="s">
         <v>27</v>
       </c>
       <c r="I48">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -4355,19 +4355,19 @@
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="P48">
         <v>2</v>
       </c>
       <c r="T48">
-        <v>250000</v>
+        <v>1000000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -4387,22 +4387,22 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>5146</v>
+        <v>7595</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C49">
-        <v>4201</v>
+        <v>5205</v>
       </c>
       <c r="D49">
-        <v>40204</v>
+        <v>50901</v>
       </c>
       <c r="E49">
         <v>9</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
         <v>64</v>
@@ -4411,7 +4411,7 @@
         <v>27</v>
       </c>
       <c r="I49">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -4420,60 +4420,57 @@
         <v>1</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49">
-        <v>55</v>
-      </c>
-      <c r="P49">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="P49" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>31</v>
       </c>
       <c r="T49">
-        <v>1000000</v>
-      </c>
-      <c r="W49">
-        <v>15000</v>
-      </c>
-      <c r="X49">
-        <v>60000</v>
-      </c>
-      <c r="Y49">
-        <v>500000</v>
+        <v>55000</v>
+      </c>
+      <c r="U49">
+        <v>2450</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>3656</v>
+        <v>10909</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>182</v>
       </c>
       <c r="C50">
-        <v>3465</v>
+        <v>4205</v>
       </c>
       <c r="D50">
-        <v>30703</v>
+        <v>40704</v>
       </c>
       <c r="E50">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G50" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I50">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -4485,22 +4482,19 @@
         <v>1</v>
       </c>
       <c r="M50" t="s">
+        <v>183</v>
+      </c>
+      <c r="N50">
+        <v>2</v>
+      </c>
+      <c r="O50">
         <v>70</v>
       </c>
-      <c r="N50">
-        <v>2</v>
-      </c>
-      <c r="O50">
-        <v>90</v>
-      </c>
       <c r="P50">
-        <v>96</v>
-      </c>
-      <c r="R50" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="T50">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -4520,22 +4514,22 @@
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>4712</v>
+        <v>5146</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51">
-        <v>5103</v>
+        <v>4201</v>
       </c>
       <c r="D51">
-        <v>50609</v>
+        <v>40204</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F51">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
         <v>64</v>
@@ -4544,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="I51">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -4556,63 +4550,57 @@
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N51">
         <v>1</v>
       </c>
       <c r="O51">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="P51">
-        <v>7</v>
-      </c>
-      <c r="T51" t="s">
-        <v>35</v>
-      </c>
-      <c r="U51" t="s">
-        <v>35</v>
-      </c>
-      <c r="V51" t="s">
-        <v>35</v>
-      </c>
-      <c r="W51" t="s">
-        <v>35</v>
-      </c>
-      <c r="X51" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="T51">
+        <v>1000000</v>
+      </c>
+      <c r="W51">
+        <v>15000</v>
+      </c>
+      <c r="X51">
+        <v>60000</v>
+      </c>
+      <c r="Y51">
+        <v>500000</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>8508</v>
+        <v>3656</v>
       </c>
       <c r="B52" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="C52">
-        <v>2202</v>
+        <v>3465</v>
       </c>
       <c r="D52">
-        <v>20111</v>
+        <v>30703</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F52">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G52" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I52">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4624,22 +4612,22 @@
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52">
-        <v>1</v>
-      </c>
-      <c r="P52" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>31</v>
+        <v>90</v>
+      </c>
+      <c r="P52">
+        <v>96</v>
+      </c>
+      <c r="R52" t="s">
+        <v>70</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -4659,102 +4647,99 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>1302</v>
+        <v>4712</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="C53">
-        <v>3111</v>
+        <v>5103</v>
       </c>
       <c r="D53">
-        <v>31101</v>
+        <v>50609</v>
       </c>
       <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H53" t="s">
+        <v>27</v>
+      </c>
+      <c r="I53">
+        <v>51</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>104</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>29</v>
+      </c>
+      <c r="P53">
         <v>7</v>
       </c>
-      <c r="F53">
-        <v>4</v>
-      </c>
-      <c r="G53" t="s">
-        <v>32</v>
-      </c>
-      <c r="H53" t="s">
-        <v>26</v>
-      </c>
-      <c r="I53">
-        <v>26</v>
-      </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53">
-        <v>1</v>
-      </c>
-      <c r="M53" t="s">
-        <v>37</v>
-      </c>
-      <c r="N53">
-        <v>2</v>
-      </c>
-      <c r="O53">
-        <v>82</v>
-      </c>
-      <c r="P53" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>31</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>40000</v>
-      </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53">
-        <v>0</v>
-      </c>
-      <c r="Y53">
-        <v>0</v>
+      <c r="T53" t="s">
+        <v>35</v>
+      </c>
+      <c r="U53" t="s">
+        <v>35</v>
+      </c>
+      <c r="V53" t="s">
+        <v>35</v>
+      </c>
+      <c r="W53" t="s">
+        <v>35</v>
+      </c>
+      <c r="X53" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>11588</v>
+        <v>8508</v>
       </c>
       <c r="B54" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C54">
-        <v>3616</v>
+        <v>2202</v>
       </c>
       <c r="D54">
-        <v>30703</v>
+        <v>20111</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H54" t="s">
         <v>27</v>
       </c>
       <c r="I54">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -4766,19 +4751,22 @@
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="N54">
         <v>1</v>
       </c>
       <c r="O54">
-        <v>78</v>
-      </c>
-      <c r="P54">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="P54" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>31</v>
       </c>
       <c r="T54">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -4798,28 +4786,31 @@
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>11382</v>
+        <v>1302</v>
       </c>
       <c r="B55" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="C55">
-        <v>3608</v>
+        <v>3111</v>
+      </c>
+      <c r="D55">
+        <v>31101</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F55">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G55" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="H55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I55">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -4831,63 +4822,66 @@
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55">
-        <v>53</v>
-      </c>
-      <c r="P55">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="P55" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>31</v>
       </c>
       <c r="T55">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="V55">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>11161</v>
+        <v>11588</v>
       </c>
       <c r="B56" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C56">
-        <v>2208</v>
+        <v>3616</v>
       </c>
       <c r="D56">
-        <v>20614</v>
+        <v>30703</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="G56" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H56" t="s">
         <v>27</v>
       </c>
       <c r="I56">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -4899,22 +4893,19 @@
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="P56">
-        <v>7</v>
-      </c>
-      <c r="R56" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -4934,102 +4925,99 @@
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>11336</v>
+        <v>11382</v>
       </c>
       <c r="B57" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C57">
-        <v>3215</v>
+        <v>3608</v>
       </c>
       <c r="D57">
-        <v>31304</v>
+        <v>30608</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H57" t="s">
         <v>27</v>
       </c>
       <c r="I57">
+        <v>94</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57" t="s">
+        <v>195</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
+      <c r="O57">
         <v>53</v>
       </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
-      <c r="L57">
-        <v>1</v>
-      </c>
-      <c r="M57" t="s">
-        <v>191</v>
-      </c>
-      <c r="N57">
-        <v>1</v>
-      </c>
-      <c r="O57">
-        <v>83</v>
-      </c>
-      <c r="P57" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>31</v>
+      <c r="P57">
+        <v>2</v>
       </c>
       <c r="T57">
-        <v>13000</v>
+        <v>200000</v>
       </c>
       <c r="U57">
-        <v>600</v>
+        <v>50000</v>
       </c>
       <c r="V57">
+        <v>50000</v>
+      </c>
+      <c r="W57">
+        <v>20000</v>
+      </c>
+      <c r="X57">
         <v>10000</v>
       </c>
-      <c r="W57">
-        <v>1600</v>
-      </c>
-      <c r="X57">
-        <v>0</v>
-      </c>
       <c r="Y57">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>2442</v>
+        <v>11161</v>
       </c>
       <c r="B58" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="C58">
-        <v>2310</v>
+        <v>2208</v>
       </c>
       <c r="D58">
-        <v>20612</v>
+        <v>20614</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I58">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -5038,25 +5026,31 @@
         <v>1</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>42</v>
+        <v>187</v>
       </c>
       <c r="N58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58">
-        <v>110</v>
-      </c>
-      <c r="P58" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="P58">
+        <v>7</v>
+      </c>
+      <c r="R58" t="s">
+        <v>188</v>
       </c>
       <c r="T58">
-        <v>15000</v>
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
       </c>
       <c r="W58">
         <v>0</v>
@@ -5070,31 +5064,31 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>8464</v>
+        <v>11336</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="C59">
-        <v>2102</v>
+        <v>3215</v>
       </c>
       <c r="D59">
-        <v>20111</v>
+        <v>31304</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H59" t="s">
         <v>27</v>
       </c>
       <c r="I59">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -5106,31 +5100,31 @@
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59">
-        <v>30</v>
-      </c>
-      <c r="P59">
-        <v>2</v>
-      </c>
-      <c r="R59" t="s">
-        <v>155</v>
+        <v>83</v>
+      </c>
+      <c r="P59" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>31</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="U59">
-        <v>1200000</v>
+        <v>600</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="X59">
         <v>0</v>
@@ -5141,31 +5135,31 @@
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>7225</v>
+        <v>2442</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="C60">
-        <v>2101</v>
+        <v>2310</v>
       </c>
       <c r="D60">
-        <v>20110</v>
+        <v>20612</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I60">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -5174,28 +5168,25 @@
         <v>1</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60">
-        <v>53</v>
-      </c>
-      <c r="P60">
-        <v>2</v>
+        <v>110</v>
+      </c>
+      <c r="P60" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>31</v>
       </c>
       <c r="T60">
-        <v>1400000</v>
-      </c>
-      <c r="U60" t="s">
-        <v>35</v>
-      </c>
-      <c r="V60">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -5209,31 +5200,31 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>13735</v>
+        <v>8464</v>
       </c>
       <c r="B61" t="s">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="C61">
-        <v>3549</v>
+        <v>2102</v>
       </c>
       <c r="D61">
-        <v>30802</v>
+        <v>20111</v>
       </c>
       <c r="E61">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F61">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H61" t="s">
         <v>27</v>
       </c>
       <c r="I61">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -5245,22 +5236,25 @@
         <v>1</v>
       </c>
       <c r="M61" t="s">
-        <v>231</v>
+        <v>153</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P61">
         <v>2</v>
       </c>
+      <c r="R61" t="s">
+        <v>154</v>
+      </c>
       <c r="T61">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -5277,32 +5271,35 @@
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>2900</v>
+        <v>7225</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="C62">
-        <v>1108</v>
+        <v>2101</v>
       </c>
       <c r="D62">
-        <v>11211</v>
+        <v>20110</v>
       </c>
       <c r="E62">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G62" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="H62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I62">
         <v>22</v>
       </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
       <c r="K62">
         <v>1</v>
       </c>
@@ -5310,22 +5307,22 @@
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>57</v>
+        <v>138</v>
+      </c>
+      <c r="N62">
+        <v>2</v>
       </c>
       <c r="O62">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="P62">
         <v>2</v>
       </c>
-      <c r="R62" t="s">
-        <v>58</v>
-      </c>
       <c r="T62">
-        <v>70000</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
+        <v>1400000</v>
+      </c>
+      <c r="U62" t="s">
+        <v>35</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -5342,31 +5339,31 @@
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>770</v>
+        <v>13735</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>229</v>
       </c>
       <c r="C63">
-        <v>5104</v>
+        <v>3549</v>
       </c>
       <c r="D63">
-        <v>50703</v>
+        <v>30802</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F63">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G63" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="H63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I63">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -5378,22 +5375,19 @@
         <v>1</v>
       </c>
       <c r="M63" t="s">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="N63">
         <v>1</v>
       </c>
       <c r="O63">
-        <v>72</v>
-      </c>
-      <c r="P63" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="P63">
+        <v>2</v>
       </c>
       <c r="T63">
-        <v>300000</v>
+        <v>35000</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -5413,34 +5407,31 @@
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5892</v>
+        <v>2900</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="C64">
-        <v>2209</v>
+        <v>1108</v>
       </c>
       <c r="D64">
-        <v>20703</v>
+        <v>11211</v>
       </c>
       <c r="E64">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G64" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="H64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I64">
-        <v>26</v>
-      </c>
-      <c r="J64">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K64">
         <v>1</v>
@@ -5449,48 +5440,63 @@
         <v>1</v>
       </c>
       <c r="M64" t="s">
-        <v>121</v>
-      </c>
-      <c r="N64">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="O64">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="R64" t="s">
+        <v>58</v>
       </c>
       <c r="T64">
-        <v>35000</v>
+        <v>70000</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10305</v>
+        <v>770</v>
       </c>
       <c r="B65" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="C65">
-        <v>4206</v>
+        <v>5104</v>
       </c>
       <c r="D65">
-        <v>40803</v>
+        <v>50703</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G65" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="H65" t="s">
         <v>26</v>
       </c>
       <c r="I65">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -5502,45 +5508,66 @@
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>171</v>
+        <v>29</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
       </c>
       <c r="O65">
-        <v>23</v>
-      </c>
-      <c r="P65">
-        <v>5</v>
-      </c>
-      <c r="R65">
-        <v>3</v>
+        <v>72</v>
+      </c>
+      <c r="P65" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>31</v>
       </c>
       <c r="T65">
-        <v>400000</v>
+        <v>300000</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>13979</v>
+        <v>5892</v>
       </c>
       <c r="B66" t="s">
-        <v>232</v>
+        <v>119</v>
       </c>
       <c r="C66">
-        <v>5611</v>
+        <v>2209</v>
+      </c>
+      <c r="D66">
+        <v>20703</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F66">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="G66" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H66" t="s">
         <v>27</v>
       </c>
       <c r="I66">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -5552,63 +5579,48 @@
         <v>1</v>
       </c>
       <c r="M66" t="s">
-        <v>233</v>
+        <v>120</v>
       </c>
       <c r="N66">
         <v>1</v>
       </c>
       <c r="O66">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="P66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>12388</v>
+        <v>10305</v>
       </c>
       <c r="B67" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="C67">
-        <v>3604</v>
+        <v>4206</v>
       </c>
       <c r="D67">
-        <v>30608</v>
+        <v>40803</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I67">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -5620,63 +5632,45 @@
         <v>1</v>
       </c>
       <c r="M67" t="s">
-        <v>220</v>
-      </c>
-      <c r="N67">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P67">
         <v>5</v>
       </c>
+      <c r="R67">
+        <v>3</v>
+      </c>
       <c r="T67">
-        <v>60000</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>6538</v>
+        <v>13979</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="C68">
-        <v>1201</v>
-      </c>
-      <c r="D68">
-        <v>10207</v>
+        <v>5611</v>
       </c>
       <c r="E68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G68" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H68" t="s">
         <v>27</v>
       </c>
       <c r="I68">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -5684,17 +5678,20 @@
       <c r="K68">
         <v>1</v>
       </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
       <c r="M68" t="s">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="P68">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T68">
         <v>0</v>
@@ -5717,31 +5714,31 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>11973</v>
+        <v>12388</v>
       </c>
       <c r="B69" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C69">
-        <v>4107</v>
+        <v>3604</v>
       </c>
       <c r="D69">
-        <v>40806</v>
+        <v>30608</v>
       </c>
       <c r="E69">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G69" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H69" t="s">
         <v>27</v>
       </c>
       <c r="I69">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -5753,19 +5750,19 @@
         <v>1</v>
       </c>
       <c r="M69" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="N69">
         <v>1</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T69">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="U69">
         <v>0</v>
@@ -5774,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="W69">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -5785,28 +5782,31 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>11374</v>
+        <v>6538</v>
       </c>
       <c r="B70" t="s">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="C70">
-        <v>3501</v>
+        <v>1201</v>
+      </c>
+      <c r="D70">
+        <v>10207</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F70">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H70" t="s">
         <v>27</v>
       </c>
       <c r="I70">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -5814,23 +5814,20 @@
       <c r="K70">
         <v>1</v>
       </c>
-      <c r="L70">
-        <v>1</v>
-      </c>
       <c r="M70" t="s">
-        <v>194</v>
+        <v>127</v>
       </c>
       <c r="N70">
         <v>2</v>
       </c>
       <c r="O70">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="P70">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T70">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -5850,31 +5847,31 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>7585</v>
+        <v>11973</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="C71">
-        <v>5205</v>
+        <v>4107</v>
       </c>
       <c r="D71">
-        <v>50901</v>
+        <v>40806</v>
       </c>
       <c r="E71">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F71">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G71" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H71" t="s">
         <v>27</v>
       </c>
       <c r="I71">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -5886,66 +5883,60 @@
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="N71">
         <v>1</v>
       </c>
       <c r="O71">
-        <v>92</v>
-      </c>
-      <c r="P71" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="P71">
+        <v>4</v>
       </c>
       <c r="T71">
-        <v>150000</v>
-      </c>
-      <c r="U71" t="s">
-        <v>35</v>
-      </c>
-      <c r="V71" t="s">
-        <v>35</v>
-      </c>
-      <c r="W71" t="s">
-        <v>35</v>
-      </c>
-      <c r="X71" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>35</v>
+        <v>40000</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>2500</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>3111</v>
+        <v>11374</v>
       </c>
       <c r="B72" t="s">
-        <v>62</v>
+        <v>192</v>
       </c>
       <c r="C72">
-        <v>6201</v>
+        <v>3501</v>
       </c>
       <c r="D72">
-        <v>60303</v>
-      </c>
-      <c r="E72">
-        <v>5</v>
+        <v>30608</v>
       </c>
       <c r="F72">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G72" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="H72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I72">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -5957,66 +5948,63 @@
         <v>1</v>
       </c>
       <c r="M72" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="N72">
         <v>2</v>
       </c>
       <c r="O72">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="P72">
         <v>2</v>
       </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
       <c r="T72">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="U72">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V72">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W72">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="X72">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="Y72">
-        <v>50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10738</v>
+        <v>7585</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="C73">
-        <v>2103</v>
+        <v>5205</v>
       </c>
       <c r="D73">
-        <v>20206</v>
+        <v>50901</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F73">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G73" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H73" t="s">
         <v>27</v>
       </c>
       <c r="I73">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -6028,66 +6016,66 @@
         <v>1</v>
       </c>
       <c r="M73" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73">
-        <v>65</v>
-      </c>
-      <c r="P73">
-        <v>96</v>
-      </c>
-      <c r="R73">
-        <v>96</v>
+        <v>92</v>
+      </c>
+      <c r="P73" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>31</v>
       </c>
       <c r="T73">
-        <v>50000</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73">
-        <v>0</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
+        <v>150000</v>
+      </c>
+      <c r="U73" t="s">
+        <v>35</v>
+      </c>
+      <c r="V73" t="s">
+        <v>35</v>
+      </c>
+      <c r="W73" t="s">
+        <v>35</v>
+      </c>
+      <c r="X73" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>4226</v>
+        <v>3111</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C74">
-        <v>3210</v>
+        <v>6201</v>
       </c>
       <c r="D74">
-        <v>30909</v>
+        <v>60303</v>
       </c>
       <c r="E74">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H74" t="s">
         <v>26</v>
       </c>
       <c r="I74">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -6099,63 +6087,66 @@
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="N74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="P74">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
       </c>
       <c r="T74">
-        <v>55000</v>
+        <v>30000</v>
       </c>
       <c r="U74">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W74">
+        <v>19000</v>
+      </c>
+      <c r="X74">
         <v>5000</v>
       </c>
-      <c r="X74">
-        <v>0</v>
-      </c>
       <c r="Y74">
-        <v>30000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>2870</v>
+        <v>10738</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="C75">
-        <v>3206</v>
+        <v>2103</v>
       </c>
       <c r="D75">
-        <v>30604</v>
+        <v>20206</v>
       </c>
       <c r="E75">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G75" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="H75" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I75">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -6167,22 +6158,22 @@
         <v>1</v>
       </c>
       <c r="M75" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="N75">
         <v>2</v>
       </c>
       <c r="O75">
-        <v>90</v>
-      </c>
-      <c r="P75" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>31</v>
+        <v>65</v>
+      </c>
+      <c r="P75">
+        <v>96</v>
+      </c>
+      <c r="R75">
+        <v>96</v>
       </c>
       <c r="T75">
-        <v>350000</v>
+        <v>50000</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -6202,10 +6193,10 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>4243</v>
+        <v>4226</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C76">
         <v>3210</v>
@@ -6217,7 +6208,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76" t="s">
         <v>64</v>
@@ -6226,7 +6217,7 @@
         <v>26</v>
       </c>
       <c r="I76">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -6238,63 +6229,63 @@
         <v>1</v>
       </c>
       <c r="M76" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N76">
         <v>1</v>
       </c>
       <c r="O76">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="P76">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="V76">
         <v>0</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X76">
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>8047</v>
+        <v>2870</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="C77">
-        <v>3104</v>
+        <v>3206</v>
       </c>
       <c r="D77">
-        <v>30512</v>
+        <v>30604</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F77">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G77" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="H77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I77">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -6303,96 +6294,93 @@
         <v>1</v>
       </c>
       <c r="L77">
-        <v>2081</v>
+        <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="N77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O77">
-        <v>75</v>
-      </c>
-      <c r="P77">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="P77" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>31</v>
       </c>
       <c r="T77">
-        <v>50000</v>
+        <v>350000</v>
       </c>
       <c r="U77">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V77">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X77">
         <v>0</v>
       </c>
       <c r="Y77">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>13570</v>
+        <v>4243</v>
       </c>
       <c r="B78" t="s">
-        <v>224</v>
+        <v>94</v>
       </c>
       <c r="C78">
-        <v>2600</v>
+        <v>3210</v>
       </c>
       <c r="D78">
-        <v>20315</v>
+        <v>30909</v>
       </c>
       <c r="E78">
+        <v>10</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78" t="s">
+        <v>64</v>
+      </c>
+      <c r="H78" t="s">
+        <v>26</v>
+      </c>
+      <c r="I78">
+        <v>53</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78" t="s">
+        <v>95</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78">
+        <v>43</v>
+      </c>
+      <c r="P78">
         <v>8</v>
       </c>
-      <c r="F78">
-        <v>44</v>
-      </c>
-      <c r="G78" t="s">
-        <v>122</v>
-      </c>
-      <c r="H78" t="s">
-        <v>27</v>
-      </c>
-      <c r="I78">
-        <v>24</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78">
-        <v>1</v>
-      </c>
-      <c r="L78">
-        <v>1</v>
-      </c>
-      <c r="M78" t="s">
-        <v>225</v>
-      </c>
-      <c r="N78">
-        <v>2</v>
-      </c>
-      <c r="O78">
-        <v>77</v>
-      </c>
-      <c r="P78" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>31</v>
-      </c>
-      <c r="R78" t="s">
-        <v>227</v>
-      </c>
       <c r="T78">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -6412,22 +6400,22 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>5517</v>
+        <v>8047</v>
       </c>
       <c r="B79" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="C79">
-        <v>3387</v>
+        <v>3104</v>
       </c>
       <c r="D79">
-        <v>30608</v>
+        <v>30512</v>
       </c>
       <c r="E79">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G79" t="s">
         <v>64</v>
@@ -6436,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="I79">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -6445,69 +6433,66 @@
         <v>1</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>2081</v>
       </c>
       <c r="M79" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="N79">
         <v>1</v>
       </c>
       <c r="O79">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P79">
-        <v>96</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X79">
         <v>0</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>11903</v>
+        <v>13570</v>
       </c>
       <c r="B80" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C80">
-        <v>4207</v>
+        <v>2600</v>
       </c>
       <c r="D80">
-        <v>40806</v>
+        <v>20315</v>
       </c>
       <c r="E80">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F80">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G80" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H80" t="s">
         <v>27</v>
       </c>
       <c r="I80">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -6519,34 +6504,37 @@
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="N80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O80">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="P80" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="Q80" t="s">
         <v>31</v>
       </c>
+      <c r="R80" t="s">
+        <v>226</v>
+      </c>
       <c r="T80">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="U80">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y80">
         <v>0</v>
@@ -6554,67 +6542,70 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>11931</v>
+        <v>5517</v>
       </c>
       <c r="B81" t="s">
-        <v>210</v>
+        <v>113</v>
       </c>
       <c r="C81">
-        <v>7203</v>
+        <v>3387</v>
       </c>
       <c r="D81">
-        <v>70403</v>
+        <v>30608</v>
       </c>
       <c r="E81">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F81">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G81" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="H81" t="s">
         <v>27</v>
       </c>
       <c r="I81">
+        <v>94</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81" t="s">
+        <v>114</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81">
         <v>72</v>
       </c>
-      <c r="J81">
-        <v>1</v>
-      </c>
-      <c r="K81">
-        <v>1</v>
-      </c>
-      <c r="L81">
-        <v>1</v>
-      </c>
-      <c r="M81" t="s">
-        <v>211</v>
-      </c>
-      <c r="N81">
-        <v>1</v>
-      </c>
-      <c r="O81">
-        <v>65</v>
-      </c>
       <c r="P81">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>115</v>
       </c>
       <c r="T81">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="U81">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="V81">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="X81">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y81">
         <v>0</v>
@@ -6622,28 +6613,31 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>14148</v>
+        <v>11903</v>
       </c>
       <c r="B82" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="C82">
-        <v>3550</v>
+        <v>4207</v>
+      </c>
+      <c r="D82">
+        <v>40806</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F82">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G82" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H82" t="s">
         <v>27</v>
       </c>
       <c r="I82">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -6652,45 +6646,63 @@
         <v>1</v>
       </c>
       <c r="L82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M82" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="N82">
         <v>1</v>
       </c>
       <c r="O82">
-        <v>79</v>
-      </c>
-      <c r="P82">
-        <v>2</v>
+        <v>64</v>
+      </c>
+      <c r="P82" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>31</v>
       </c>
       <c r="T82">
         <v>50000</v>
       </c>
+      <c r="U82">
+        <v>30000</v>
+      </c>
+      <c r="V82">
+        <v>20000</v>
+      </c>
+      <c r="W82">
+        <v>3000</v>
+      </c>
+      <c r="X82">
+        <v>10000</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>8293</v>
+        <v>11931</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="C83">
-        <v>7105</v>
+        <v>7203</v>
       </c>
       <c r="D83">
-        <v>70601</v>
+        <v>70403</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F83">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G83" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="H83" t="s">
         <v>27</v>
@@ -6705,37 +6717,34 @@
         <v>1</v>
       </c>
       <c r="L83">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O83">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="P83">
-        <v>8</v>
-      </c>
-      <c r="R83" t="s">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y83">
         <v>0</v>
@@ -6743,79 +6752,203 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84">
+        <v>14148</v>
+      </c>
+      <c r="B84" t="s">
+        <v>235</v>
+      </c>
+      <c r="C84">
+        <v>3550</v>
+      </c>
+      <c r="D84">
+        <v>30802</v>
+      </c>
+      <c r="E84">
+        <v>5</v>
+      </c>
+      <c r="F84">
+        <v>50</v>
+      </c>
+      <c r="G84" t="s">
+        <v>121</v>
+      </c>
+      <c r="H84" t="s">
+        <v>27</v>
+      </c>
+      <c r="I84">
+        <v>56</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>4</v>
+      </c>
+      <c r="M84" t="s">
+        <v>236</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84">
+        <v>79</v>
+      </c>
+      <c r="P84">
+        <v>2</v>
+      </c>
+      <c r="T84">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>8293</v>
+      </c>
+      <c r="B85" t="s">
+        <v>149</v>
+      </c>
+      <c r="C85">
+        <v>7105</v>
+      </c>
+      <c r="D85">
+        <v>70601</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>11</v>
+      </c>
+      <c r="G85" t="s">
+        <v>64</v>
+      </c>
+      <c r="H85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85">
+        <v>72</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>8</v>
+      </c>
+      <c r="M85" t="s">
+        <v>150</v>
+      </c>
+      <c r="N85">
+        <v>2</v>
+      </c>
+      <c r="O85">
+        <v>72</v>
+      </c>
+      <c r="P85">
+        <v>8</v>
+      </c>
+      <c r="R85" t="s">
+        <v>151</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>3918</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86">
+        <v>7310</v>
+      </c>
+      <c r="D86">
+        <v>70813</v>
+      </c>
+      <c r="E86">
+        <v>4</v>
+      </c>
+      <c r="F86">
+        <v>9</v>
+      </c>
+      <c r="G86" t="s">
+        <v>64</v>
+      </c>
+      <c r="H86" t="s">
+        <v>26</v>
+      </c>
+      <c r="I86">
+        <v>72</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
         <v>82</v>
       </c>
-      <c r="C84">
-        <v>7310</v>
-      </c>
-      <c r="D84">
-        <v>70813</v>
-      </c>
-      <c r="E84">
-        <v>4</v>
-      </c>
-      <c r="F84">
-        <v>9</v>
-      </c>
-      <c r="G84" t="s">
-        <v>64</v>
-      </c>
-      <c r="H84" t="s">
-        <v>26</v>
-      </c>
-      <c r="I84">
-        <v>72</v>
-      </c>
-      <c r="J84">
-        <v>1</v>
-      </c>
-      <c r="K84">
-        <v>1</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84" t="s">
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86">
+        <v>95</v>
+      </c>
+      <c r="P86" t="s">
         <v>83</v>
       </c>
-      <c r="N84">
-        <v>1</v>
-      </c>
-      <c r="O84">
-        <v>95</v>
-      </c>
-      <c r="P84" t="s">
+      <c r="Q86" t="s">
         <v>84</v>
       </c>
-      <c r="Q84" t="s">
-        <v>85</v>
-      </c>
-      <c r="T84">
+      <c r="T86">
         <v>30000</v>
       </c>
-      <c r="U84">
+      <c r="U86">
         <v>20000</v>
       </c>
-      <c r="V84">
+      <c r="V86">
         <v>25000</v>
       </c>
-      <c r="W84">
+      <c r="W86">
         <v>5000</v>
       </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
+      <c r="X86">
+        <v>0</v>
+      </c>
+      <c r="Y86">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y4146">
-    <sortCondition ref="M1:M4146"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y4284">
+    <sortCondition ref="M1:M4284"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
